--- a/synuclein_inclusion_biogenesis_2024/image_analysis/galectin/23525_3K_dox_inclusions.xlsx
+++ b/synuclein_inclusion_biogenesis_2024/image_analysis/galectin/23525_3K_dox_inclusions.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Inclusions</t>
+          <t>Inclusion</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -460,7 +460,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
         <v>123</v>
@@ -476,7 +476,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
         <v>24</v>
@@ -492,7 +492,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
         <v>324</v>
@@ -508,7 +508,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
         <v>42</v>
@@ -524,7 +524,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>55</v>
@@ -540,7 +540,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
         <v>9</v>
@@ -556,7 +556,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
         <v>18</v>
@@ -572,7 +572,7 @@
         <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
         <v>7</v>
@@ -588,7 +588,7 @@
         <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
         <v>86</v>
@@ -604,7 +604,7 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
         <v>36</v>
@@ -620,7 +620,7 @@
         <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
         <v>128</v>
@@ -636,7 +636,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
         <v>44</v>
@@ -652,7 +652,7 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
         <v>19</v>
@@ -668,7 +668,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
         <v>54</v>
@@ -684,7 +684,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
         <v>27</v>
@@ -700,7 +700,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
         <v>25</v>
@@ -716,7 +716,7 @@
         <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
         <v>28</v>
@@ -732,7 +732,7 @@
         <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
         <v>24</v>
@@ -748,7 +748,7 @@
         <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
         <v>1085</v>
@@ -764,7 +764,7 @@
         <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
         <v>55</v>
@@ -780,7 +780,7 @@
         <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
         <v>208</v>
@@ -796,7 +796,7 @@
         <v>5</v>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
         <v>7</v>
@@ -812,7 +812,7 @@
         <v>5</v>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
         <v>12</v>
@@ -828,7 +828,7 @@
         <v>5</v>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
         <v>6</v>
@@ -844,7 +844,7 @@
         <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
         <v>29</v>
@@ -860,7 +860,7 @@
         <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D27" t="n">
         <v>33</v>
@@ -876,7 +876,7 @@
         <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D28" t="n">
         <v>213</v>
@@ -892,7 +892,7 @@
         <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D29" t="n">
         <v>38</v>
@@ -908,7 +908,7 @@
         <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D30" t="n">
         <v>9</v>
@@ -924,7 +924,7 @@
         <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D31" t="n">
         <v>5</v>
@@ -940,7 +940,7 @@
         <v>6</v>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
         <v>26</v>
@@ -956,7 +956,7 @@
         <v>6</v>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
         <v>34</v>
@@ -972,7 +972,7 @@
         <v>6</v>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D34" t="n">
         <v>219</v>
@@ -988,7 +988,7 @@
         <v>7</v>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
         <v>31</v>
@@ -1004,7 +1004,7 @@
         <v>7</v>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
         <v>59</v>
@@ -1020,7 +1020,7 @@
         <v>7</v>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D37" t="n">
         <v>68</v>
@@ -1036,7 +1036,7 @@
         <v>7</v>
       </c>
       <c r="C38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D38" t="n">
         <v>15</v>
@@ -1052,7 +1052,7 @@
         <v>7</v>
       </c>
       <c r="C39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D39" t="n">
         <v>260</v>
@@ -1068,7 +1068,7 @@
         <v>8</v>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
         <v>5</v>
@@ -1084,7 +1084,7 @@
         <v>8</v>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
         <v>42</v>
@@ -1100,7 +1100,7 @@
         <v>8</v>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D42" t="n">
         <v>39</v>
@@ -1116,7 +1116,7 @@
         <v>8</v>
       </c>
       <c r="C43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D43" t="n">
         <v>43</v>
@@ -1132,7 +1132,7 @@
         <v>8</v>
       </c>
       <c r="C44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D44" t="n">
         <v>7</v>
@@ -1148,7 +1148,7 @@
         <v>8</v>
       </c>
       <c r="C45" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D45" t="n">
         <v>50</v>
@@ -1164,7 +1164,7 @@
         <v>8</v>
       </c>
       <c r="C46" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D46" t="n">
         <v>10</v>
@@ -1180,7 +1180,7 @@
         <v>8</v>
       </c>
       <c r="C47" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D47" t="n">
         <v>111</v>
@@ -1196,7 +1196,7 @@
         <v>8</v>
       </c>
       <c r="C48" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D48" t="n">
         <v>7</v>
@@ -1212,7 +1212,7 @@
         <v>9</v>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
         <v>225</v>
@@ -1228,7 +1228,7 @@
         <v>9</v>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D50" t="n">
         <v>11</v>
@@ -1244,7 +1244,7 @@
         <v>9</v>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D51" t="n">
         <v>6</v>
@@ -1260,7 +1260,7 @@
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D52" t="n">
         <v>8</v>
@@ -1276,7 +1276,7 @@
         <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
         <v>5</v>
@@ -1292,7 +1292,7 @@
         <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D54" t="n">
         <v>5</v>
@@ -1308,7 +1308,7 @@
         <v>3</v>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
         <v>342</v>
@@ -1324,7 +1324,7 @@
         <v>3</v>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D56" t="n">
         <v>99</v>
@@ -1340,7 +1340,7 @@
         <v>3</v>
       </c>
       <c r="C57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D57" t="n">
         <v>16</v>
@@ -1356,7 +1356,7 @@
         <v>3</v>
       </c>
       <c r="C58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D58" t="n">
         <v>334</v>
@@ -1372,7 +1372,7 @@
         <v>3</v>
       </c>
       <c r="C59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D59" t="n">
         <v>524</v>
@@ -1388,7 +1388,7 @@
         <v>3</v>
       </c>
       <c r="C60" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D60" t="n">
         <v>111</v>
@@ -1404,7 +1404,7 @@
         <v>4</v>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D61" t="n">
         <v>5</v>
@@ -1420,7 +1420,7 @@
         <v>4</v>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D62" t="n">
         <v>5</v>
@@ -1436,7 +1436,7 @@
         <v>4</v>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D63" t="n">
         <v>62</v>
@@ -1452,7 +1452,7 @@
         <v>4</v>
       </c>
       <c r="C64" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D64" t="n">
         <v>42</v>
@@ -1468,7 +1468,7 @@
         <v>4</v>
       </c>
       <c r="C65" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D65" t="n">
         <v>14</v>
@@ -1484,7 +1484,7 @@
         <v>4</v>
       </c>
       <c r="C66" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D66" t="n">
         <v>16</v>
@@ -1500,7 +1500,7 @@
         <v>4</v>
       </c>
       <c r="C67" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D67" t="n">
         <v>154</v>
@@ -1516,7 +1516,7 @@
         <v>4</v>
       </c>
       <c r="C68" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D68" t="n">
         <v>6</v>
@@ -1532,7 +1532,7 @@
         <v>4</v>
       </c>
       <c r="C69" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D69" t="n">
         <v>18</v>
@@ -1548,7 +1548,7 @@
         <v>5</v>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D70" t="n">
         <v>43</v>
@@ -1564,7 +1564,7 @@
         <v>5</v>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D71" t="n">
         <v>53</v>
@@ -1580,7 +1580,7 @@
         <v>5</v>
       </c>
       <c r="C72" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D72" t="n">
         <v>270</v>
@@ -1596,7 +1596,7 @@
         <v>5</v>
       </c>
       <c r="C73" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D73" t="n">
         <v>24</v>
@@ -1612,7 +1612,7 @@
         <v>6</v>
       </c>
       <c r="C74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D74" t="n">
         <v>1077</v>
@@ -1628,7 +1628,7 @@
         <v>6</v>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D75" t="n">
         <v>430</v>
@@ -1644,7 +1644,7 @@
         <v>7</v>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D76" t="n">
         <v>52</v>
@@ -1660,7 +1660,7 @@
         <v>7</v>
       </c>
       <c r="C77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D77" t="n">
         <v>7</v>
@@ -1676,7 +1676,7 @@
         <v>7</v>
       </c>
       <c r="C78" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D78" t="n">
         <v>10</v>
@@ -1692,7 +1692,7 @@
         <v>7</v>
       </c>
       <c r="C79" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D79" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
         <v>8</v>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D80" t="n">
         <v>10</v>
@@ -1724,7 +1724,7 @@
         <v>8</v>
       </c>
       <c r="C81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D81" t="n">
         <v>17</v>
@@ -1740,7 +1740,7 @@
         <v>8</v>
       </c>
       <c r="C82" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D82" t="n">
         <v>62</v>
@@ -1756,7 +1756,7 @@
         <v>8</v>
       </c>
       <c r="C83" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D83" t="n">
         <v>18</v>
@@ -1772,7 +1772,7 @@
         <v>8</v>
       </c>
       <c r="C84" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D84" t="n">
         <v>8</v>
@@ -1788,7 +1788,7 @@
         <v>8</v>
       </c>
       <c r="C85" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D85" t="n">
         <v>7</v>
@@ -1804,7 +1804,7 @@
         <v>8</v>
       </c>
       <c r="C86" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D86" t="n">
         <v>34</v>
@@ -1820,7 +1820,7 @@
         <v>8</v>
       </c>
       <c r="C87" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D87" t="n">
         <v>19</v>
@@ -1836,7 +1836,7 @@
         <v>8</v>
       </c>
       <c r="C88" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D88" t="n">
         <v>5</v>
@@ -1852,7 +1852,7 @@
         <v>9</v>
       </c>
       <c r="C89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D89" t="n">
         <v>16</v>
@@ -1868,7 +1868,7 @@
         <v>9</v>
       </c>
       <c r="C90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D90" t="n">
         <v>11</v>
@@ -1884,7 +1884,7 @@
         <v>9</v>
       </c>
       <c r="C91" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D91" t="n">
         <v>51</v>
@@ -1900,7 +1900,7 @@
         <v>9</v>
       </c>
       <c r="C92" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D92" t="n">
         <v>11</v>
@@ -1916,7 +1916,7 @@
         <v>9</v>
       </c>
       <c r="C93" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D93" t="n">
         <v>5</v>
@@ -1932,7 +1932,7 @@
         <v>9</v>
       </c>
       <c r="C94" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D94" t="n">
         <v>11</v>
@@ -1948,7 +1948,7 @@
         <v>9</v>
       </c>
       <c r="C95" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D95" t="n">
         <v>15</v>
@@ -1964,7 +1964,7 @@
         <v>9</v>
       </c>
       <c r="C96" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D96" t="n">
         <v>7</v>
@@ -1980,7 +1980,7 @@
         <v>1</v>
       </c>
       <c r="C97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D97" t="n">
         <v>14</v>
@@ -1996,7 +1996,7 @@
         <v>1</v>
       </c>
       <c r="C98" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D98" t="n">
         <v>90</v>
@@ -2012,7 +2012,7 @@
         <v>1</v>
       </c>
       <c r="C99" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D99" t="n">
         <v>5</v>
@@ -2028,7 +2028,7 @@
         <v>1</v>
       </c>
       <c r="C100" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D100" t="n">
         <v>20</v>
@@ -2044,7 +2044,7 @@
         <v>1</v>
       </c>
       <c r="C101" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D101" t="n">
         <v>110</v>
@@ -2060,7 +2060,7 @@
         <v>1</v>
       </c>
       <c r="C102" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D102" t="n">
         <v>6</v>
@@ -2076,7 +2076,7 @@
         <v>1</v>
       </c>
       <c r="C103" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D103" t="n">
         <v>17</v>
@@ -2092,7 +2092,7 @@
         <v>1</v>
       </c>
       <c r="C104" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D104" t="n">
         <v>133</v>
@@ -2108,7 +2108,7 @@
         <v>2</v>
       </c>
       <c r="C105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D105" t="n">
         <v>12</v>
@@ -2124,7 +2124,7 @@
         <v>2</v>
       </c>
       <c r="C106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D106" t="n">
         <v>30</v>
@@ -2140,7 +2140,7 @@
         <v>2</v>
       </c>
       <c r="C107" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D107" t="n">
         <v>52</v>
@@ -2156,7 +2156,7 @@
         <v>2</v>
       </c>
       <c r="C108" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D108" t="n">
         <v>82</v>
@@ -2172,7 +2172,7 @@
         <v>2</v>
       </c>
       <c r="C109" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D109" t="n">
         <v>14</v>
@@ -2188,7 +2188,7 @@
         <v>2</v>
       </c>
       <c r="C110" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D110" t="n">
         <v>16</v>
@@ -2204,7 +2204,7 @@
         <v>2</v>
       </c>
       <c r="C111" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D111" t="n">
         <v>143</v>
@@ -2220,7 +2220,7 @@
         <v>2</v>
       </c>
       <c r="C112" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D112" t="n">
         <v>154</v>
@@ -2236,7 +2236,7 @@
         <v>1</v>
       </c>
       <c r="C113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D113" t="n">
         <v>438</v>
@@ -2252,7 +2252,7 @@
         <v>1</v>
       </c>
       <c r="C114" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D114" t="n">
         <v>21</v>
@@ -2268,7 +2268,7 @@
         <v>2</v>
       </c>
       <c r="C115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D115" t="n">
         <v>6</v>
@@ -2284,7 +2284,7 @@
         <v>2</v>
       </c>
       <c r="C116" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D116" t="n">
         <v>7</v>
@@ -2300,7 +2300,7 @@
         <v>2</v>
       </c>
       <c r="C117" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D117" t="n">
         <v>16</v>
@@ -2316,7 +2316,7 @@
         <v>2</v>
       </c>
       <c r="C118" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D118" t="n">
         <v>6</v>
@@ -2332,7 +2332,7 @@
         <v>2</v>
       </c>
       <c r="C119" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D119" t="n">
         <v>7</v>
@@ -2348,7 +2348,7 @@
         <v>2</v>
       </c>
       <c r="C120" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D120" t="n">
         <v>8</v>
@@ -2364,7 +2364,7 @@
         <v>2</v>
       </c>
       <c r="C121" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D121" t="n">
         <v>7</v>
@@ -2380,7 +2380,7 @@
         <v>2</v>
       </c>
       <c r="C122" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D122" t="n">
         <v>9</v>
@@ -2396,7 +2396,7 @@
         <v>3</v>
       </c>
       <c r="C123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D123" t="n">
         <v>6</v>
@@ -2412,7 +2412,7 @@
         <v>3</v>
       </c>
       <c r="C124" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D124" t="n">
         <v>5</v>
@@ -2428,7 +2428,7 @@
         <v>3</v>
       </c>
       <c r="C125" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D125" t="n">
         <v>470</v>
@@ -2444,7 +2444,7 @@
         <v>3</v>
       </c>
       <c r="C126" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D126" t="n">
         <v>5</v>
@@ -2460,7 +2460,7 @@
         <v>3</v>
       </c>
       <c r="C127" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D127" t="n">
         <v>6</v>
@@ -2476,7 +2476,7 @@
         <v>4</v>
       </c>
       <c r="C128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D128" t="n">
         <v>22</v>
@@ -2492,7 +2492,7 @@
         <v>4</v>
       </c>
       <c r="C129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D129" t="n">
         <v>201</v>
@@ -2508,7 +2508,7 @@
         <v>4</v>
       </c>
       <c r="C130" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D130" t="n">
         <v>63</v>
@@ -2524,7 +2524,7 @@
         <v>5</v>
       </c>
       <c r="C131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D131" t="n">
         <v>46</v>
@@ -2540,7 +2540,7 @@
         <v>5</v>
       </c>
       <c r="C132" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D132" t="n">
         <v>59</v>
@@ -2556,7 +2556,7 @@
         <v>5</v>
       </c>
       <c r="C133" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D133" t="n">
         <v>16</v>
@@ -2572,7 +2572,7 @@
         <v>6</v>
       </c>
       <c r="C134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D134" t="n">
         <v>144</v>
@@ -2588,7 +2588,7 @@
         <v>6</v>
       </c>
       <c r="C135" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D135" t="n">
         <v>147</v>
@@ -2604,7 +2604,7 @@
         <v>6</v>
       </c>
       <c r="C136" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D136" t="n">
         <v>121</v>
@@ -2620,7 +2620,7 @@
         <v>6</v>
       </c>
       <c r="C137" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D137" t="n">
         <v>64</v>
@@ -2636,7 +2636,7 @@
         <v>7</v>
       </c>
       <c r="C138" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D138" t="n">
         <v>9</v>
@@ -2652,7 +2652,7 @@
         <v>7</v>
       </c>
       <c r="C139" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D139" t="n">
         <v>16</v>
@@ -2668,7 +2668,7 @@
         <v>7</v>
       </c>
       <c r="C140" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D140" t="n">
         <v>81</v>
@@ -2684,7 +2684,7 @@
         <v>7</v>
       </c>
       <c r="C141" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D141" t="n">
         <v>6</v>
@@ -2700,7 +2700,7 @@
         <v>7</v>
       </c>
       <c r="C142" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D142" t="n">
         <v>56</v>
@@ -2716,7 +2716,7 @@
         <v>7</v>
       </c>
       <c r="C143" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D143" t="n">
         <v>49</v>
@@ -2732,7 +2732,7 @@
         <v>8</v>
       </c>
       <c r="C144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D144" t="n">
         <v>8</v>
@@ -2748,7 +2748,7 @@
         <v>8</v>
       </c>
       <c r="C145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D145" t="n">
         <v>12</v>
@@ -2764,7 +2764,7 @@
         <v>8</v>
       </c>
       <c r="C146" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D146" t="n">
         <v>7</v>
@@ -2780,7 +2780,7 @@
         <v>8</v>
       </c>
       <c r="C147" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D147" t="n">
         <v>13</v>
@@ -2796,7 +2796,7 @@
         <v>8</v>
       </c>
       <c r="C148" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D148" t="n">
         <v>22</v>
@@ -2812,7 +2812,7 @@
         <v>9</v>
       </c>
       <c r="C149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D149" t="n">
         <v>75</v>
@@ -2828,7 +2828,7 @@
         <v>10</v>
       </c>
       <c r="C150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D150" t="n">
         <v>58</v>
@@ -2844,7 +2844,7 @@
         <v>10</v>
       </c>
       <c r="C151" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D151" t="n">
         <v>84</v>
@@ -2860,7 +2860,7 @@
         <v>10</v>
       </c>
       <c r="C152" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D152" t="n">
         <v>26</v>
@@ -2876,7 +2876,7 @@
         <v>1</v>
       </c>
       <c r="C153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D153" t="n">
         <v>6</v>
@@ -2892,7 +2892,7 @@
         <v>1</v>
       </c>
       <c r="C154" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D154" t="n">
         <v>9</v>
@@ -2908,7 +2908,7 @@
         <v>1</v>
       </c>
       <c r="C155" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D155" t="n">
         <v>18</v>
@@ -2924,7 +2924,7 @@
         <v>1</v>
       </c>
       <c r="C156" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D156" t="n">
         <v>27</v>
@@ -2940,7 +2940,7 @@
         <v>2</v>
       </c>
       <c r="C157" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D157" t="n">
         <v>613</v>
@@ -2956,7 +2956,7 @@
         <v>2</v>
       </c>
       <c r="C158" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D158" t="n">
         <v>13</v>
@@ -2972,7 +2972,7 @@
         <v>2</v>
       </c>
       <c r="C159" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D159" t="n">
         <v>6</v>
@@ -2988,7 +2988,7 @@
         <v>2</v>
       </c>
       <c r="C160" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D160" t="n">
         <v>37</v>
@@ -3004,7 +3004,7 @@
         <v>2</v>
       </c>
       <c r="C161" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D161" t="n">
         <v>12</v>
@@ -3020,7 +3020,7 @@
         <v>2</v>
       </c>
       <c r="C162" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D162" t="n">
         <v>60</v>
@@ -3036,7 +3036,7 @@
         <v>2</v>
       </c>
       <c r="C163" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D163" t="n">
         <v>35</v>
@@ -3052,7 +3052,7 @@
         <v>2</v>
       </c>
       <c r="C164" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D164" t="n">
         <v>65</v>
@@ -3068,7 +3068,7 @@
         <v>2</v>
       </c>
       <c r="C165" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D165" t="n">
         <v>151</v>
@@ -3084,7 +3084,7 @@
         <v>2</v>
       </c>
       <c r="C166" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D166" t="n">
         <v>59</v>
@@ -3100,7 +3100,7 @@
         <v>2</v>
       </c>
       <c r="C167" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D167" t="n">
         <v>31</v>
@@ -3116,7 +3116,7 @@
         <v>3</v>
       </c>
       <c r="C168" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D168" t="n">
         <v>1993</v>
@@ -3132,7 +3132,7 @@
         <v>3</v>
       </c>
       <c r="C169" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D169" t="n">
         <v>18</v>
@@ -3148,7 +3148,7 @@
         <v>4</v>
       </c>
       <c r="C170" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D170" t="n">
         <v>68</v>
@@ -3164,7 +3164,7 @@
         <v>4</v>
       </c>
       <c r="C171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D171" t="n">
         <v>6</v>
@@ -3180,7 +3180,7 @@
         <v>4</v>
       </c>
       <c r="C172" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D172" t="n">
         <v>66</v>
@@ -3196,7 +3196,7 @@
         <v>5</v>
       </c>
       <c r="C173" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D173" t="n">
         <v>285</v>
@@ -3212,7 +3212,7 @@
         <v>5</v>
       </c>
       <c r="C174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D174" t="n">
         <v>97</v>
@@ -3228,7 +3228,7 @@
         <v>5</v>
       </c>
       <c r="C175" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D175" t="n">
         <v>5</v>
@@ -3244,7 +3244,7 @@
         <v>6</v>
       </c>
       <c r="C176" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D176" t="n">
         <v>82</v>
@@ -3260,7 +3260,7 @@
         <v>6</v>
       </c>
       <c r="C177" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D177" t="n">
         <v>27</v>
@@ -3276,7 +3276,7 @@
         <v>6</v>
       </c>
       <c r="C178" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D178" t="n">
         <v>549</v>
@@ -3292,7 +3292,7 @@
         <v>6</v>
       </c>
       <c r="C179" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D179" t="n">
         <v>116</v>
@@ -3308,7 +3308,7 @@
         <v>6</v>
       </c>
       <c r="C180" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D180" t="n">
         <v>7</v>
@@ -3324,7 +3324,7 @@
         <v>6</v>
       </c>
       <c r="C181" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D181" t="n">
         <v>53</v>
@@ -3340,7 +3340,7 @@
         <v>7</v>
       </c>
       <c r="C182" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D182" t="n">
         <v>152</v>
@@ -3356,7 +3356,7 @@
         <v>7</v>
       </c>
       <c r="C183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D183" t="n">
         <v>8</v>
@@ -3372,7 +3372,7 @@
         <v>8</v>
       </c>
       <c r="C184" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D184" t="n">
         <v>24</v>
@@ -3388,7 +3388,7 @@
         <v>8</v>
       </c>
       <c r="C185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D185" t="n">
         <v>9</v>
@@ -3404,7 +3404,7 @@
         <v>8</v>
       </c>
       <c r="C186" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D186" t="n">
         <v>25</v>
@@ -3420,7 +3420,7 @@
         <v>9</v>
       </c>
       <c r="C187" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D187" t="n">
         <v>29</v>
@@ -3436,7 +3436,7 @@
         <v>9</v>
       </c>
       <c r="C188" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D188" t="n">
         <v>9</v>
@@ -3452,7 +3452,7 @@
         <v>9</v>
       </c>
       <c r="C189" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D189" t="n">
         <v>12</v>
@@ -3468,7 +3468,7 @@
         <v>9</v>
       </c>
       <c r="C190" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D190" t="n">
         <v>5</v>
@@ -3484,7 +3484,7 @@
         <v>9</v>
       </c>
       <c r="C191" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D191" t="n">
         <v>32</v>
@@ -3500,7 +3500,7 @@
         <v>9</v>
       </c>
       <c r="C192" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D192" t="n">
         <v>32</v>
@@ -3516,7 +3516,7 @@
         <v>10</v>
       </c>
       <c r="C193" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D193" t="n">
         <v>87</v>
@@ -3532,7 +3532,7 @@
         <v>10</v>
       </c>
       <c r="C194" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D194" t="n">
         <v>41</v>
@@ -3548,7 +3548,7 @@
         <v>10</v>
       </c>
       <c r="C195" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D195" t="n">
         <v>43</v>
@@ -3564,7 +3564,7 @@
         <v>10</v>
       </c>
       <c r="C196" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D196" t="n">
         <v>37</v>
@@ -3580,7 +3580,7 @@
         <v>10</v>
       </c>
       <c r="C197" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D197" t="n">
         <v>30</v>
@@ -3596,7 +3596,7 @@
         <v>10</v>
       </c>
       <c r="C198" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D198" t="n">
         <v>26</v>
@@ -3612,7 +3612,7 @@
         <v>10</v>
       </c>
       <c r="C199" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D199" t="n">
         <v>98</v>
@@ -3628,7 +3628,7 @@
         <v>10</v>
       </c>
       <c r="C200" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D200" t="n">
         <v>38</v>
@@ -3644,7 +3644,7 @@
         <v>10</v>
       </c>
       <c r="C201" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D201" t="n">
         <v>13</v>
@@ -3660,7 +3660,7 @@
         <v>1</v>
       </c>
       <c r="C202" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D202" t="n">
         <v>28</v>
@@ -3676,7 +3676,7 @@
         <v>1</v>
       </c>
       <c r="C203" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D203" t="n">
         <v>14</v>
@@ -3692,7 +3692,7 @@
         <v>2</v>
       </c>
       <c r="C204" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D204" t="n">
         <v>10</v>
@@ -3708,7 +3708,7 @@
         <v>2</v>
       </c>
       <c r="C205" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D205" t="n">
         <v>18</v>
@@ -3724,7 +3724,7 @@
         <v>3</v>
       </c>
       <c r="C206" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D206" t="n">
         <v>7</v>
@@ -3740,7 +3740,7 @@
         <v>3</v>
       </c>
       <c r="C207" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D207" t="n">
         <v>342</v>
@@ -3756,7 +3756,7 @@
         <v>3</v>
       </c>
       <c r="C208" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D208" t="n">
         <v>40</v>
@@ -3772,7 +3772,7 @@
         <v>3</v>
       </c>
       <c r="C209" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D209" t="n">
         <v>6</v>
@@ -3788,7 +3788,7 @@
         <v>3</v>
       </c>
       <c r="C210" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D210" t="n">
         <v>30</v>
@@ -3804,7 +3804,7 @@
         <v>3</v>
       </c>
       <c r="C211" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D211" t="n">
         <v>61</v>
@@ -3820,7 +3820,7 @@
         <v>3</v>
       </c>
       <c r="C212" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D212" t="n">
         <v>67</v>
@@ -3836,7 +3836,7 @@
         <v>4</v>
       </c>
       <c r="C213" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D213" t="n">
         <v>8</v>
@@ -3852,7 +3852,7 @@
         <v>4</v>
       </c>
       <c r="C214" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D214" t="n">
         <v>60</v>
@@ -3868,7 +3868,7 @@
         <v>4</v>
       </c>
       <c r="C215" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D215" t="n">
         <v>180</v>
@@ -3884,7 +3884,7 @@
         <v>5</v>
       </c>
       <c r="C216" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D216" t="n">
         <v>506</v>
@@ -3900,7 +3900,7 @@
         <v>5</v>
       </c>
       <c r="C217" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D217" t="n">
         <v>5</v>
@@ -3916,7 +3916,7 @@
         <v>5</v>
       </c>
       <c r="C218" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D218" t="n">
         <v>55</v>
@@ -3932,7 +3932,7 @@
         <v>5</v>
       </c>
       <c r="C219" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D219" t="n">
         <v>90</v>
@@ -3948,7 +3948,7 @@
         <v>5</v>
       </c>
       <c r="C220" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D220" t="n">
         <v>146</v>
@@ -3964,7 +3964,7 @@
         <v>6</v>
       </c>
       <c r="C221" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D221" t="n">
         <v>377</v>
@@ -3980,7 +3980,7 @@
         <v>6</v>
       </c>
       <c r="C222" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D222" t="n">
         <v>123</v>
@@ -3996,7 +3996,7 @@
         <v>6</v>
       </c>
       <c r="C223" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D223" t="n">
         <v>36</v>
@@ -4012,7 +4012,7 @@
         <v>6</v>
       </c>
       <c r="C224" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D224" t="n">
         <v>16</v>
@@ -4028,7 +4028,7 @@
         <v>6</v>
       </c>
       <c r="C225" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D225" t="n">
         <v>11</v>
@@ -4044,7 +4044,7 @@
         <v>6</v>
       </c>
       <c r="C226" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D226" t="n">
         <v>456</v>
@@ -4060,7 +4060,7 @@
         <v>6</v>
       </c>
       <c r="C227" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D227" t="n">
         <v>13</v>
@@ -4076,7 +4076,7 @@
         <v>7</v>
       </c>
       <c r="C228" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D228" t="n">
         <v>12</v>
@@ -4092,7 +4092,7 @@
         <v>7</v>
       </c>
       <c r="C229" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D229" t="n">
         <v>13</v>
@@ -4108,7 +4108,7 @@
         <v>7</v>
       </c>
       <c r="C230" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D230" t="n">
         <v>5</v>
@@ -4124,7 +4124,7 @@
         <v>7</v>
       </c>
       <c r="C231" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D231" t="n">
         <v>70</v>
@@ -4140,7 +4140,7 @@
         <v>7</v>
       </c>
       <c r="C232" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D232" t="n">
         <v>10</v>
@@ -4156,7 +4156,7 @@
         <v>7</v>
       </c>
       <c r="C233" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D233" t="n">
         <v>5</v>
@@ -4172,7 +4172,7 @@
         <v>7</v>
       </c>
       <c r="C234" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D234" t="n">
         <v>8</v>
@@ -4188,7 +4188,7 @@
         <v>7</v>
       </c>
       <c r="C235" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D235" t="n">
         <v>29</v>
@@ -4204,7 +4204,7 @@
         <v>8</v>
       </c>
       <c r="C236" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D236" t="n">
         <v>137</v>
@@ -4220,7 +4220,7 @@
         <v>8</v>
       </c>
       <c r="C237" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D237" t="n">
         <v>32</v>
@@ -4236,7 +4236,7 @@
         <v>8</v>
       </c>
       <c r="C238" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D238" t="n">
         <v>9</v>
@@ -4252,7 +4252,7 @@
         <v>8</v>
       </c>
       <c r="C239" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D239" t="n">
         <v>29</v>
@@ -4268,7 +4268,7 @@
         <v>8</v>
       </c>
       <c r="C240" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D240" t="n">
         <v>18</v>
@@ -4284,7 +4284,7 @@
         <v>8</v>
       </c>
       <c r="C241" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D241" t="n">
         <v>18</v>
@@ -4300,7 +4300,7 @@
         <v>8</v>
       </c>
       <c r="C242" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D242" t="n">
         <v>25</v>
@@ -4316,7 +4316,7 @@
         <v>8</v>
       </c>
       <c r="C243" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D243" t="n">
         <v>67</v>
@@ -4332,7 +4332,7 @@
         <v>9</v>
       </c>
       <c r="C244" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D244" t="n">
         <v>12</v>
@@ -4348,7 +4348,7 @@
         <v>9</v>
       </c>
       <c r="C245" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D245" t="n">
         <v>23</v>
@@ -4364,7 +4364,7 @@
         <v>9</v>
       </c>
       <c r="C246" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D246" t="n">
         <v>505</v>
@@ -4380,7 +4380,7 @@
         <v>9</v>
       </c>
       <c r="C247" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D247" t="n">
         <v>6</v>
@@ -4396,7 +4396,7 @@
         <v>1</v>
       </c>
       <c r="C248" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D248" t="n">
         <v>14</v>
@@ -4412,7 +4412,7 @@
         <v>1</v>
       </c>
       <c r="C249" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D249" t="n">
         <v>251</v>
@@ -4428,7 +4428,7 @@
         <v>1</v>
       </c>
       <c r="C250" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D250" t="n">
         <v>456</v>
@@ -4444,7 +4444,7 @@
         <v>1</v>
       </c>
       <c r="C251" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D251" t="n">
         <v>32</v>
@@ -4460,7 +4460,7 @@
         <v>2</v>
       </c>
       <c r="C252" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D252" t="n">
         <v>1017</v>
@@ -4476,7 +4476,7 @@
         <v>2</v>
       </c>
       <c r="C253" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D253" t="n">
         <v>49</v>
@@ -4492,7 +4492,7 @@
         <v>2</v>
       </c>
       <c r="C254" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D254" t="n">
         <v>55</v>
@@ -4508,7 +4508,7 @@
         <v>3</v>
       </c>
       <c r="C255" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D255" t="n">
         <v>485</v>
@@ -4524,7 +4524,7 @@
         <v>1</v>
       </c>
       <c r="C256" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D256" t="n">
         <v>52</v>
@@ -4540,7 +4540,7 @@
         <v>1</v>
       </c>
       <c r="C257" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D257" t="n">
         <v>13</v>
@@ -4556,7 +4556,7 @@
         <v>1</v>
       </c>
       <c r="C258" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D258" t="n">
         <v>28</v>
@@ -4572,7 +4572,7 @@
         <v>1</v>
       </c>
       <c r="C259" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D259" t="n">
         <v>124</v>
@@ -4588,7 +4588,7 @@
         <v>1</v>
       </c>
       <c r="C260" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D260" t="n">
         <v>296</v>
@@ -4604,7 +4604,7 @@
         <v>1</v>
       </c>
       <c r="C261" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D261" t="n">
         <v>6</v>
@@ -4620,7 +4620,7 @@
         <v>1</v>
       </c>
       <c r="C262" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D262" t="n">
         <v>239</v>
@@ -4636,7 +4636,7 @@
         <v>2</v>
       </c>
       <c r="C263" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D263" t="n">
         <v>17</v>
@@ -4652,7 +4652,7 @@
         <v>2</v>
       </c>
       <c r="C264" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D264" t="n">
         <v>7</v>
@@ -4668,7 +4668,7 @@
         <v>2</v>
       </c>
       <c r="C265" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D265" t="n">
         <v>119</v>
@@ -4684,7 +4684,7 @@
         <v>2</v>
       </c>
       <c r="C266" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D266" t="n">
         <v>66</v>
@@ -4700,7 +4700,7 @@
         <v>2</v>
       </c>
       <c r="C267" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D267" t="n">
         <v>44</v>
@@ -4716,7 +4716,7 @@
         <v>2</v>
       </c>
       <c r="C268" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D268" t="n">
         <v>13</v>
@@ -4732,7 +4732,7 @@
         <v>2</v>
       </c>
       <c r="C269" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D269" t="n">
         <v>102</v>
@@ -4748,7 +4748,7 @@
         <v>2</v>
       </c>
       <c r="C270" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D270" t="n">
         <v>61</v>
@@ -4764,7 +4764,7 @@
         <v>2</v>
       </c>
       <c r="C271" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D271" t="n">
         <v>266</v>
@@ -4780,7 +4780,7 @@
         <v>2</v>
       </c>
       <c r="C272" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D272" t="n">
         <v>12</v>
@@ -4796,7 +4796,7 @@
         <v>2</v>
       </c>
       <c r="C273" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D273" t="n">
         <v>17</v>
@@ -4812,7 +4812,7 @@
         <v>2</v>
       </c>
       <c r="C274" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D274" t="n">
         <v>20</v>
@@ -4828,7 +4828,7 @@
         <v>2</v>
       </c>
       <c r="C275" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D275" t="n">
         <v>22</v>
@@ -4844,7 +4844,7 @@
         <v>2</v>
       </c>
       <c r="C276" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D276" t="n">
         <v>15</v>
@@ -4860,7 +4860,7 @@
         <v>2</v>
       </c>
       <c r="C277" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D277" t="n">
         <v>44</v>
@@ -4876,7 +4876,7 @@
         <v>2</v>
       </c>
       <c r="C278" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D278" t="n">
         <v>7</v>
@@ -4892,7 +4892,7 @@
         <v>1</v>
       </c>
       <c r="C279" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D279" t="n">
         <v>13</v>
@@ -4908,7 +4908,7 @@
         <v>2</v>
       </c>
       <c r="C280" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D280" t="n">
         <v>44</v>
@@ -4924,7 +4924,7 @@
         <v>2</v>
       </c>
       <c r="C281" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D281" t="n">
         <v>32</v>
@@ -4940,7 +4940,7 @@
         <v>2</v>
       </c>
       <c r="C282" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D282" t="n">
         <v>5</v>
@@ -4956,7 +4956,7 @@
         <v>3</v>
       </c>
       <c r="C283" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D283" t="n">
         <v>9</v>
@@ -4972,7 +4972,7 @@
         <v>3</v>
       </c>
       <c r="C284" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D284" t="n">
         <v>146</v>
@@ -4988,7 +4988,7 @@
         <v>3</v>
       </c>
       <c r="C285" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D285" t="n">
         <v>29</v>
@@ -5004,7 +5004,7 @@
         <v>3</v>
       </c>
       <c r="C286" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D286" t="n">
         <v>12</v>
@@ -5020,7 +5020,7 @@
         <v>4</v>
       </c>
       <c r="C287" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D287" t="n">
         <v>5</v>
@@ -5036,7 +5036,7 @@
         <v>4</v>
       </c>
       <c r="C288" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D288" t="n">
         <v>37</v>
@@ -5052,7 +5052,7 @@
         <v>4</v>
       </c>
       <c r="C289" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D289" t="n">
         <v>5</v>
@@ -5068,7 +5068,7 @@
         <v>4</v>
       </c>
       <c r="C290" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D290" t="n">
         <v>23</v>
@@ -5084,7 +5084,7 @@
         <v>4</v>
       </c>
       <c r="C291" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D291" t="n">
         <v>7</v>
@@ -5100,7 +5100,7 @@
         <v>4</v>
       </c>
       <c r="C292" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D292" t="n">
         <v>8</v>
@@ -5116,7 +5116,7 @@
         <v>4</v>
       </c>
       <c r="C293" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D293" t="n">
         <v>6</v>
@@ -5132,7 +5132,7 @@
         <v>5</v>
       </c>
       <c r="C294" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D294" t="n">
         <v>1321</v>
@@ -5148,7 +5148,7 @@
         <v>5</v>
       </c>
       <c r="C295" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D295" t="n">
         <v>5</v>
@@ -5164,7 +5164,7 @@
         <v>5</v>
       </c>
       <c r="C296" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D296" t="n">
         <v>42</v>
@@ -5180,7 +5180,7 @@
         <v>5</v>
       </c>
       <c r="C297" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D297" t="n">
         <v>16</v>
@@ -5196,7 +5196,7 @@
         <v>5</v>
       </c>
       <c r="C298" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D298" t="n">
         <v>26</v>
@@ -5212,7 +5212,7 @@
         <v>5</v>
       </c>
       <c r="C299" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D299" t="n">
         <v>11</v>
@@ -5228,7 +5228,7 @@
         <v>6</v>
       </c>
       <c r="C300" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D300" t="n">
         <v>27</v>
@@ -5244,7 +5244,7 @@
         <v>6</v>
       </c>
       <c r="C301" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D301" t="n">
         <v>8</v>
@@ -5260,7 +5260,7 @@
         <v>6</v>
       </c>
       <c r="C302" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D302" t="n">
         <v>24</v>
@@ -5276,7 +5276,7 @@
         <v>6</v>
       </c>
       <c r="C303" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D303" t="n">
         <v>54</v>
@@ -5292,7 +5292,7 @@
         <v>6</v>
       </c>
       <c r="C304" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D304" t="n">
         <v>13</v>
@@ -5308,7 +5308,7 @@
         <v>6</v>
       </c>
       <c r="C305" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D305" t="n">
         <v>5</v>
@@ -5324,7 +5324,7 @@
         <v>6</v>
       </c>
       <c r="C306" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D306" t="n">
         <v>9</v>
@@ -5340,7 +5340,7 @@
         <v>1</v>
       </c>
       <c r="C307" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D307" t="n">
         <v>34</v>
@@ -5356,7 +5356,7 @@
         <v>1</v>
       </c>
       <c r="C308" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D308" t="n">
         <v>9</v>
@@ -5372,7 +5372,7 @@
         <v>1</v>
       </c>
       <c r="C309" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D309" t="n">
         <v>14</v>
@@ -5388,7 +5388,7 @@
         <v>1</v>
       </c>
       <c r="C310" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D310" t="n">
         <v>17</v>
@@ -5404,7 +5404,7 @@
         <v>1</v>
       </c>
       <c r="C311" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D311" t="n">
         <v>54</v>
@@ -5420,7 +5420,7 @@
         <v>1</v>
       </c>
       <c r="C312" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D312" t="n">
         <v>32</v>
@@ -5436,7 +5436,7 @@
         <v>2</v>
       </c>
       <c r="C313" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D313" t="n">
         <v>12</v>
@@ -5452,7 +5452,7 @@
         <v>3</v>
       </c>
       <c r="C314" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D314" t="n">
         <v>10</v>
@@ -5468,7 +5468,7 @@
         <v>3</v>
       </c>
       <c r="C315" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D315" t="n">
         <v>32</v>
@@ -5484,7 +5484,7 @@
         <v>3</v>
       </c>
       <c r="C316" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D316" t="n">
         <v>16</v>
@@ -5500,7 +5500,7 @@
         <v>3</v>
       </c>
       <c r="C317" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D317" t="n">
         <v>6</v>
@@ -5516,7 +5516,7 @@
         <v>3</v>
       </c>
       <c r="C318" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D318" t="n">
         <v>5</v>
@@ -5532,7 +5532,7 @@
         <v>3</v>
       </c>
       <c r="C319" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D319" t="n">
         <v>27</v>
@@ -5548,7 +5548,7 @@
         <v>3</v>
       </c>
       <c r="C320" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D320" t="n">
         <v>15</v>
@@ -5564,7 +5564,7 @@
         <v>3</v>
       </c>
       <c r="C321" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D321" t="n">
         <v>8</v>
@@ -5580,7 +5580,7 @@
         <v>1</v>
       </c>
       <c r="C322" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D322" t="n">
         <v>9</v>
@@ -5596,7 +5596,7 @@
         <v>1</v>
       </c>
       <c r="C323" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D323" t="n">
         <v>7</v>
@@ -5612,7 +5612,7 @@
         <v>1</v>
       </c>
       <c r="C324" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D324" t="n">
         <v>10</v>
@@ -5628,7 +5628,7 @@
         <v>1</v>
       </c>
       <c r="C325" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D325" t="n">
         <v>9</v>
@@ -5644,7 +5644,7 @@
         <v>1</v>
       </c>
       <c r="C326" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D326" t="n">
         <v>22</v>
@@ -5660,7 +5660,7 @@
         <v>1</v>
       </c>
       <c r="C327" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D327" t="n">
         <v>18</v>
@@ -5676,7 +5676,7 @@
         <v>1</v>
       </c>
       <c r="C328" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D328" t="n">
         <v>68</v>
@@ -5692,7 +5692,7 @@
         <v>2</v>
       </c>
       <c r="C329" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D329" t="n">
         <v>528</v>
@@ -5708,7 +5708,7 @@
         <v>2</v>
       </c>
       <c r="C330" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D330" t="n">
         <v>8</v>
@@ -5724,7 +5724,7 @@
         <v>2</v>
       </c>
       <c r="C331" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D331" t="n">
         <v>124</v>
@@ -5740,7 +5740,7 @@
         <v>2</v>
       </c>
       <c r="C332" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D332" t="n">
         <v>314</v>
@@ -5756,7 +5756,7 @@
         <v>2</v>
       </c>
       <c r="C333" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D333" t="n">
         <v>6</v>
@@ -5772,7 +5772,7 @@
         <v>2</v>
       </c>
       <c r="C334" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D334" t="n">
         <v>9</v>
@@ -5788,7 +5788,7 @@
         <v>2</v>
       </c>
       <c r="C335" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D335" t="n">
         <v>14</v>
@@ -5804,7 +5804,7 @@
         <v>2</v>
       </c>
       <c r="C336" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D336" t="n">
         <v>105</v>
@@ -5820,7 +5820,7 @@
         <v>2</v>
       </c>
       <c r="C337" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D337" t="n">
         <v>7</v>
@@ -5836,7 +5836,7 @@
         <v>2</v>
       </c>
       <c r="C338" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D338" t="n">
         <v>14</v>
@@ -5852,7 +5852,7 @@
         <v>3</v>
       </c>
       <c r="C339" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D339" t="n">
         <v>64</v>
@@ -5868,7 +5868,7 @@
         <v>3</v>
       </c>
       <c r="C340" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D340" t="n">
         <v>60</v>
@@ -5884,7 +5884,7 @@
         <v>3</v>
       </c>
       <c r="C341" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D341" t="n">
         <v>33</v>
@@ -5900,7 +5900,7 @@
         <v>3</v>
       </c>
       <c r="C342" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D342" t="n">
         <v>171</v>
@@ -5916,7 +5916,7 @@
         <v>3</v>
       </c>
       <c r="C343" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D343" t="n">
         <v>19</v>
@@ -5932,7 +5932,7 @@
         <v>3</v>
       </c>
       <c r="C344" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D344" t="n">
         <v>146</v>
@@ -5948,7 +5948,7 @@
         <v>3</v>
       </c>
       <c r="C345" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D345" t="n">
         <v>14</v>
@@ -5964,7 +5964,7 @@
         <v>3</v>
       </c>
       <c r="C346" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D346" t="n">
         <v>18</v>
@@ -5980,7 +5980,7 @@
         <v>4</v>
       </c>
       <c r="C347" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D347" t="n">
         <v>8</v>
@@ -5996,7 +5996,7 @@
         <v>4</v>
       </c>
       <c r="C348" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D348" t="n">
         <v>75</v>
@@ -6012,7 +6012,7 @@
         <v>4</v>
       </c>
       <c r="C349" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D349" t="n">
         <v>18</v>
@@ -6028,7 +6028,7 @@
         <v>4</v>
       </c>
       <c r="C350" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D350" t="n">
         <v>15</v>
@@ -6044,7 +6044,7 @@
         <v>5</v>
       </c>
       <c r="C351" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D351" t="n">
         <v>353</v>
@@ -6060,7 +6060,7 @@
         <v>5</v>
       </c>
       <c r="C352" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D352" t="n">
         <v>434</v>
@@ -6076,7 +6076,7 @@
         <v>5</v>
       </c>
       <c r="C353" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D353" t="n">
         <v>104</v>
@@ -6092,7 +6092,7 @@
         <v>5</v>
       </c>
       <c r="C354" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D354" t="n">
         <v>59</v>
@@ -6108,7 +6108,7 @@
         <v>5</v>
       </c>
       <c r="C355" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D355" t="n">
         <v>56</v>
@@ -6124,7 +6124,7 @@
         <v>5</v>
       </c>
       <c r="C356" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D356" t="n">
         <v>5</v>
@@ -6140,7 +6140,7 @@
         <v>5</v>
       </c>
       <c r="C357" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D357" t="n">
         <v>66</v>
@@ -6156,7 +6156,7 @@
         <v>5</v>
       </c>
       <c r="C358" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D358" t="n">
         <v>9</v>
@@ -6172,7 +6172,7 @@
         <v>6</v>
       </c>
       <c r="C359" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D359" t="n">
         <v>8</v>
@@ -6188,7 +6188,7 @@
         <v>6</v>
       </c>
       <c r="C360" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D360" t="n">
         <v>6</v>
@@ -6204,7 +6204,7 @@
         <v>7</v>
       </c>
       <c r="C361" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D361" t="n">
         <v>10</v>
@@ -6220,7 +6220,7 @@
         <v>7</v>
       </c>
       <c r="C362" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D362" t="n">
         <v>14</v>
@@ -6236,7 +6236,7 @@
         <v>7</v>
       </c>
       <c r="C363" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D363" t="n">
         <v>6</v>
@@ -6252,7 +6252,7 @@
         <v>1</v>
       </c>
       <c r="C364" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D364" t="n">
         <v>89</v>
@@ -6268,7 +6268,7 @@
         <v>1</v>
       </c>
       <c r="C365" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D365" t="n">
         <v>12</v>
@@ -6284,7 +6284,7 @@
         <v>1</v>
       </c>
       <c r="C366" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D366" t="n">
         <v>19</v>
@@ -6300,7 +6300,7 @@
         <v>1</v>
       </c>
       <c r="C367" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D367" t="n">
         <v>29</v>
@@ -6316,7 +6316,7 @@
         <v>1</v>
       </c>
       <c r="C368" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D368" t="n">
         <v>5</v>
@@ -6332,7 +6332,7 @@
         <v>2</v>
       </c>
       <c r="C369" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D369" t="n">
         <v>8</v>
@@ -6348,7 +6348,7 @@
         <v>2</v>
       </c>
       <c r="C370" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D370" t="n">
         <v>266</v>
@@ -6364,7 +6364,7 @@
         <v>2</v>
       </c>
       <c r="C371" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D371" t="n">
         <v>18</v>
@@ -6380,7 +6380,7 @@
         <v>2</v>
       </c>
       <c r="C372" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D372" t="n">
         <v>35</v>
@@ -6396,7 +6396,7 @@
         <v>3</v>
       </c>
       <c r="C373" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D373" t="n">
         <v>64</v>
@@ -6412,7 +6412,7 @@
         <v>3</v>
       </c>
       <c r="C374" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D374" t="n">
         <v>15</v>
@@ -6428,7 +6428,7 @@
         <v>3</v>
       </c>
       <c r="C375" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D375" t="n">
         <v>43</v>
@@ -6444,7 +6444,7 @@
         <v>3</v>
       </c>
       <c r="C376" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D376" t="n">
         <v>7</v>
@@ -6460,7 +6460,7 @@
         <v>3</v>
       </c>
       <c r="C377" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D377" t="n">
         <v>28</v>
@@ -6476,7 +6476,7 @@
         <v>4</v>
       </c>
       <c r="C378" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D378" t="n">
         <v>22</v>
@@ -6492,7 +6492,7 @@
         <v>4</v>
       </c>
       <c r="C379" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D379" t="n">
         <v>205</v>
@@ -6508,7 +6508,7 @@
         <v>4</v>
       </c>
       <c r="C380" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D380" t="n">
         <v>8</v>
@@ -6524,7 +6524,7 @@
         <v>4</v>
       </c>
       <c r="C381" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D381" t="n">
         <v>55</v>
@@ -6540,7 +6540,7 @@
         <v>1</v>
       </c>
       <c r="C382" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D382" t="n">
         <v>500</v>
@@ -6556,7 +6556,7 @@
         <v>1</v>
       </c>
       <c r="C383" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D383" t="n">
         <v>10</v>
@@ -6572,7 +6572,7 @@
         <v>1</v>
       </c>
       <c r="C384" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D384" t="n">
         <v>24</v>
@@ -6588,7 +6588,7 @@
         <v>1</v>
       </c>
       <c r="C385" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D385" t="n">
         <v>332</v>
@@ -6604,7 +6604,7 @@
         <v>1</v>
       </c>
       <c r="C386" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D386" t="n">
         <v>45</v>
@@ -6620,7 +6620,7 @@
         <v>1</v>
       </c>
       <c r="C387" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D387" t="n">
         <v>14</v>
@@ -6636,7 +6636,7 @@
         <v>2</v>
       </c>
       <c r="C388" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D388" t="n">
         <v>7</v>
@@ -6652,7 +6652,7 @@
         <v>2</v>
       </c>
       <c r="C389" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D389" t="n">
         <v>72</v>
@@ -6668,7 +6668,7 @@
         <v>1</v>
       </c>
       <c r="C390" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D390" t="n">
         <v>47</v>
@@ -6684,7 +6684,7 @@
         <v>1</v>
       </c>
       <c r="C391" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D391" t="n">
         <v>13</v>
@@ -6700,7 +6700,7 @@
         <v>1</v>
       </c>
       <c r="C392" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D392" t="n">
         <v>49</v>
@@ -6716,7 +6716,7 @@
         <v>1</v>
       </c>
       <c r="C393" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D393" t="n">
         <v>15</v>
@@ -6732,7 +6732,7 @@
         <v>1</v>
       </c>
       <c r="C394" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D394" t="n">
         <v>18</v>
@@ -6748,7 +6748,7 @@
         <v>1</v>
       </c>
       <c r="C395" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D395" t="n">
         <v>61</v>
@@ -6764,7 +6764,7 @@
         <v>1</v>
       </c>
       <c r="C396" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D396" t="n">
         <v>55</v>
@@ -6780,7 +6780,7 @@
         <v>1</v>
       </c>
       <c r="C397" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D397" t="n">
         <v>5</v>
@@ -6796,7 +6796,7 @@
         <v>1</v>
       </c>
       <c r="C398" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D398" t="n">
         <v>54</v>
@@ -6812,7 +6812,7 @@
         <v>1</v>
       </c>
       <c r="C399" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D399" t="n">
         <v>76</v>
@@ -6828,7 +6828,7 @@
         <v>1</v>
       </c>
       <c r="C400" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D400" t="n">
         <v>21</v>
@@ -6844,7 +6844,7 @@
         <v>1</v>
       </c>
       <c r="C401" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D401" t="n">
         <v>59</v>
@@ -6860,7 +6860,7 @@
         <v>1</v>
       </c>
       <c r="C402" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D402" t="n">
         <v>16</v>
@@ -6876,7 +6876,7 @@
         <v>1</v>
       </c>
       <c r="C403" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D403" t="n">
         <v>86</v>
@@ -6892,7 +6892,7 @@
         <v>1</v>
       </c>
       <c r="C404" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D404" t="n">
         <v>7</v>
@@ -6908,7 +6908,7 @@
         <v>1</v>
       </c>
       <c r="C405" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D405" t="n">
         <v>9</v>
@@ -6924,7 +6924,7 @@
         <v>2</v>
       </c>
       <c r="C406" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D406" t="n">
         <v>135</v>
@@ -6940,7 +6940,7 @@
         <v>2</v>
       </c>
       <c r="C407" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D407" t="n">
         <v>133</v>
@@ -6956,7 +6956,7 @@
         <v>2</v>
       </c>
       <c r="C408" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D408" t="n">
         <v>41</v>
@@ -6972,7 +6972,7 @@
         <v>2</v>
       </c>
       <c r="C409" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D409" t="n">
         <v>370</v>
@@ -6988,7 +6988,7 @@
         <v>2</v>
       </c>
       <c r="C410" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D410" t="n">
         <v>11</v>
@@ -7004,7 +7004,7 @@
         <v>2</v>
       </c>
       <c r="C411" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D411" t="n">
         <v>38</v>
@@ -7020,7 +7020,7 @@
         <v>3</v>
       </c>
       <c r="C412" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D412" t="n">
         <v>14</v>
@@ -7036,7 +7036,7 @@
         <v>3</v>
       </c>
       <c r="C413" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D413" t="n">
         <v>65</v>
@@ -7052,7 +7052,7 @@
         <v>3</v>
       </c>
       <c r="C414" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D414" t="n">
         <v>6</v>
@@ -7068,7 +7068,7 @@
         <v>3</v>
       </c>
       <c r="C415" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D415" t="n">
         <v>121</v>
@@ -7084,7 +7084,7 @@
         <v>3</v>
       </c>
       <c r="C416" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D416" t="n">
         <v>92</v>
@@ -7100,7 +7100,7 @@
         <v>3</v>
       </c>
       <c r="C417" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D417" t="n">
         <v>13</v>
@@ -7116,7 +7116,7 @@
         <v>3</v>
       </c>
       <c r="C418" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D418" t="n">
         <v>14</v>
@@ -7132,7 +7132,7 @@
         <v>4</v>
       </c>
       <c r="C419" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D419" t="n">
         <v>13</v>
@@ -7148,7 +7148,7 @@
         <v>4</v>
       </c>
       <c r="C420" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D420" t="n">
         <v>118</v>
@@ -7164,7 +7164,7 @@
         <v>4</v>
       </c>
       <c r="C421" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D421" t="n">
         <v>19</v>
@@ -7180,7 +7180,7 @@
         <v>4</v>
       </c>
       <c r="C422" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D422" t="n">
         <v>34</v>
@@ -7196,7 +7196,7 @@
         <v>4</v>
       </c>
       <c r="C423" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D423" t="n">
         <v>533</v>
@@ -7212,7 +7212,7 @@
         <v>4</v>
       </c>
       <c r="C424" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D424" t="n">
         <v>20</v>
@@ -7228,7 +7228,7 @@
         <v>4</v>
       </c>
       <c r="C425" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D425" t="n">
         <v>13</v>
@@ -7244,7 +7244,7 @@
         <v>1</v>
       </c>
       <c r="C426" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D426" t="n">
         <v>66</v>
@@ -7260,7 +7260,7 @@
         <v>1</v>
       </c>
       <c r="C427" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D427" t="n">
         <v>22</v>
@@ -7276,7 +7276,7 @@
         <v>1</v>
       </c>
       <c r="C428" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D428" t="n">
         <v>21</v>
@@ -7292,7 +7292,7 @@
         <v>1</v>
       </c>
       <c r="C429" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D429" t="n">
         <v>142</v>
@@ -7308,7 +7308,7 @@
         <v>1</v>
       </c>
       <c r="C430" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D430" t="n">
         <v>226</v>
@@ -7324,7 +7324,7 @@
         <v>1</v>
       </c>
       <c r="C431" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D431" t="n">
         <v>15</v>
@@ -7340,7 +7340,7 @@
         <v>1</v>
       </c>
       <c r="C432" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D432" t="n">
         <v>45</v>
@@ -7356,7 +7356,7 @@
         <v>1</v>
       </c>
       <c r="C433" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D433" t="n">
         <v>8</v>
@@ -7372,7 +7372,7 @@
         <v>1</v>
       </c>
       <c r="C434" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D434" t="n">
         <v>50</v>
@@ -7388,7 +7388,7 @@
         <v>2</v>
       </c>
       <c r="C435" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D435" t="n">
         <v>26</v>
@@ -7404,7 +7404,7 @@
         <v>2</v>
       </c>
       <c r="C436" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D436" t="n">
         <v>6</v>
@@ -7420,7 +7420,7 @@
         <v>2</v>
       </c>
       <c r="C437" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D437" t="n">
         <v>14</v>
@@ -7436,7 +7436,7 @@
         <v>3</v>
       </c>
       <c r="C438" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D438" t="n">
         <v>278</v>
@@ -7452,7 +7452,7 @@
         <v>3</v>
       </c>
       <c r="C439" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D439" t="n">
         <v>8</v>
@@ -7468,7 +7468,7 @@
         <v>3</v>
       </c>
       <c r="C440" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D440" t="n">
         <v>24</v>
@@ -7484,7 +7484,7 @@
         <v>3</v>
       </c>
       <c r="C441" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D441" t="n">
         <v>9</v>
@@ -7500,7 +7500,7 @@
         <v>3</v>
       </c>
       <c r="C442" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D442" t="n">
         <v>24</v>
@@ -7516,7 +7516,7 @@
         <v>3</v>
       </c>
       <c r="C443" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D443" t="n">
         <v>17</v>
@@ -7532,7 +7532,7 @@
         <v>3</v>
       </c>
       <c r="C444" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D444" t="n">
         <v>72</v>
@@ -7548,7 +7548,7 @@
         <v>4</v>
       </c>
       <c r="C445" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D445" t="n">
         <v>5</v>
@@ -7564,7 +7564,7 @@
         <v>4</v>
       </c>
       <c r="C446" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D446" t="n">
         <v>26</v>
@@ -7580,7 +7580,7 @@
         <v>4</v>
       </c>
       <c r="C447" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D447" t="n">
         <v>28</v>
@@ -7596,7 +7596,7 @@
         <v>4</v>
       </c>
       <c r="C448" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D448" t="n">
         <v>10</v>
@@ -7612,7 +7612,7 @@
         <v>4</v>
       </c>
       <c r="C449" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D449" t="n">
         <v>15</v>
@@ -7628,7 +7628,7 @@
         <v>4</v>
       </c>
       <c r="C450" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D450" t="n">
         <v>50</v>
@@ -7644,7 +7644,7 @@
         <v>4</v>
       </c>
       <c r="C451" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D451" t="n">
         <v>14</v>
@@ -7660,7 +7660,7 @@
         <v>4</v>
       </c>
       <c r="C452" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D452" t="n">
         <v>21</v>
@@ -7676,7 +7676,7 @@
         <v>4</v>
       </c>
       <c r="C453" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D453" t="n">
         <v>152</v>
@@ -7692,7 +7692,7 @@
         <v>4</v>
       </c>
       <c r="C454" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D454" t="n">
         <v>105</v>
@@ -7708,7 +7708,7 @@
         <v>4</v>
       </c>
       <c r="C455" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D455" t="n">
         <v>12</v>
@@ -7724,7 +7724,7 @@
         <v>5</v>
       </c>
       <c r="C456" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D456" t="n">
         <v>101</v>
@@ -7740,7 +7740,7 @@
         <v>5</v>
       </c>
       <c r="C457" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D457" t="n">
         <v>63</v>
@@ -7756,7 +7756,7 @@
         <v>5</v>
       </c>
       <c r="C458" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D458" t="n">
         <v>43</v>
@@ -7772,7 +7772,7 @@
         <v>5</v>
       </c>
       <c r="C459" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D459" t="n">
         <v>5</v>
@@ -7788,7 +7788,7 @@
         <v>6</v>
       </c>
       <c r="C460" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D460" t="n">
         <v>32</v>
@@ -7804,7 +7804,7 @@
         <v>6</v>
       </c>
       <c r="C461" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D461" t="n">
         <v>17</v>
@@ -7820,7 +7820,7 @@
         <v>6</v>
       </c>
       <c r="C462" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D462" t="n">
         <v>13</v>
@@ -7836,7 +7836,7 @@
         <v>6</v>
       </c>
       <c r="C463" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D463" t="n">
         <v>59</v>
@@ -7852,7 +7852,7 @@
         <v>6</v>
       </c>
       <c r="C464" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D464" t="n">
         <v>54</v>
@@ -7868,7 +7868,7 @@
         <v>6</v>
       </c>
       <c r="C465" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D465" t="n">
         <v>377</v>
@@ -7884,7 +7884,7 @@
         <v>6</v>
       </c>
       <c r="C466" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D466" t="n">
         <v>7</v>
@@ -7900,7 +7900,7 @@
         <v>7</v>
       </c>
       <c r="C467" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D467" t="n">
         <v>22</v>
@@ -7916,7 +7916,7 @@
         <v>7</v>
       </c>
       <c r="C468" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D468" t="n">
         <v>15</v>
@@ -7932,7 +7932,7 @@
         <v>7</v>
       </c>
       <c r="C469" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D469" t="n">
         <v>24</v>
@@ -7948,7 +7948,7 @@
         <v>7</v>
       </c>
       <c r="C470" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D470" t="n">
         <v>707</v>
@@ -7964,7 +7964,7 @@
         <v>7</v>
       </c>
       <c r="C471" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D471" t="n">
         <v>118</v>
@@ -7980,7 +7980,7 @@
         <v>8</v>
       </c>
       <c r="C472" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D472" t="n">
         <v>779</v>
@@ -7996,7 +7996,7 @@
         <v>8</v>
       </c>
       <c r="C473" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D473" t="n">
         <v>29</v>
@@ -8012,7 +8012,7 @@
         <v>8</v>
       </c>
       <c r="C474" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D474" t="n">
         <v>14</v>
@@ -8028,7 +8028,7 @@
         <v>8</v>
       </c>
       <c r="C475" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D475" t="n">
         <v>16</v>
@@ -8044,7 +8044,7 @@
         <v>1</v>
       </c>
       <c r="C476" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D476" t="n">
         <v>32</v>
@@ -8060,7 +8060,7 @@
         <v>1</v>
       </c>
       <c r="C477" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D477" t="n">
         <v>5</v>
@@ -8076,7 +8076,7 @@
         <v>1</v>
       </c>
       <c r="C478" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D478" t="n">
         <v>40</v>
@@ -8092,7 +8092,7 @@
         <v>1</v>
       </c>
       <c r="C479" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D479" t="n">
         <v>47</v>
@@ -8108,7 +8108,7 @@
         <v>1</v>
       </c>
       <c r="C480" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D480" t="n">
         <v>137</v>
@@ -8124,7 +8124,7 @@
         <v>1</v>
       </c>
       <c r="C481" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D481" t="n">
         <v>15</v>
@@ -8140,7 +8140,7 @@
         <v>1</v>
       </c>
       <c r="C482" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D482" t="n">
         <v>6</v>
@@ -8156,7 +8156,7 @@
         <v>1</v>
       </c>
       <c r="C483" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D483" t="n">
         <v>107</v>
@@ -8172,7 +8172,7 @@
         <v>2</v>
       </c>
       <c r="C484" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D484" t="n">
         <v>1341</v>
@@ -8188,7 +8188,7 @@
         <v>2</v>
       </c>
       <c r="C485" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D485" t="n">
         <v>9</v>
@@ -8204,7 +8204,7 @@
         <v>3</v>
       </c>
       <c r="C486" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D486" t="n">
         <v>1285</v>
@@ -8220,7 +8220,7 @@
         <v>3</v>
       </c>
       <c r="C487" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D487" t="n">
         <v>5</v>
@@ -8236,7 +8236,7 @@
         <v>4</v>
       </c>
       <c r="C488" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D488" t="n">
         <v>78</v>
@@ -8252,7 +8252,7 @@
         <v>4</v>
       </c>
       <c r="C489" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D489" t="n">
         <v>6</v>
@@ -8268,7 +8268,7 @@
         <v>4</v>
       </c>
       <c r="C490" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D490" t="n">
         <v>10</v>
@@ -8284,7 +8284,7 @@
         <v>4</v>
       </c>
       <c r="C491" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D491" t="n">
         <v>12</v>
@@ -8300,7 +8300,7 @@
         <v>4</v>
       </c>
       <c r="C492" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D492" t="n">
         <v>5</v>
@@ -8316,7 +8316,7 @@
         <v>4</v>
       </c>
       <c r="C493" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D493" t="n">
         <v>10</v>
@@ -8332,7 +8332,7 @@
         <v>4</v>
       </c>
       <c r="C494" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D494" t="n">
         <v>7</v>
@@ -8348,7 +8348,7 @@
         <v>4</v>
       </c>
       <c r="C495" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D495" t="n">
         <v>9</v>
@@ -8364,7 +8364,7 @@
         <v>4</v>
       </c>
       <c r="C496" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D496" t="n">
         <v>27</v>
@@ -8380,7 +8380,7 @@
         <v>4</v>
       </c>
       <c r="C497" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D497" t="n">
         <v>13</v>
@@ -8396,7 +8396,7 @@
         <v>4</v>
       </c>
       <c r="C498" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D498" t="n">
         <v>23</v>
@@ -8412,7 +8412,7 @@
         <v>5</v>
       </c>
       <c r="C499" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D499" t="n">
         <v>351</v>
@@ -8428,7 +8428,7 @@
         <v>5</v>
       </c>
       <c r="C500" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D500" t="n">
         <v>53</v>
@@ -8444,7 +8444,7 @@
         <v>5</v>
       </c>
       <c r="C501" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D501" t="n">
         <v>68</v>
@@ -8460,7 +8460,7 @@
         <v>5</v>
       </c>
       <c r="C502" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D502" t="n">
         <v>238</v>
@@ -8476,7 +8476,7 @@
         <v>5</v>
       </c>
       <c r="C503" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D503" t="n">
         <v>26</v>
@@ -8492,7 +8492,7 @@
         <v>1</v>
       </c>
       <c r="C504" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D504" t="n">
         <v>15</v>
@@ -8508,7 +8508,7 @@
         <v>1</v>
       </c>
       <c r="C505" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D505" t="n">
         <v>23</v>
@@ -8524,7 +8524,7 @@
         <v>1</v>
       </c>
       <c r="C506" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D506" t="n">
         <v>12</v>
@@ -8540,7 +8540,7 @@
         <v>1</v>
       </c>
       <c r="C507" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D507" t="n">
         <v>12</v>
@@ -8556,7 +8556,7 @@
         <v>1</v>
       </c>
       <c r="C508" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D508" t="n">
         <v>12</v>
@@ -8572,7 +8572,7 @@
         <v>1</v>
       </c>
       <c r="C509" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D509" t="n">
         <v>92</v>
@@ -8588,7 +8588,7 @@
         <v>2</v>
       </c>
       <c r="C510" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D510" t="n">
         <v>73</v>
@@ -8604,7 +8604,7 @@
         <v>2</v>
       </c>
       <c r="C511" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D511" t="n">
         <v>317</v>
@@ -8620,7 +8620,7 @@
         <v>2</v>
       </c>
       <c r="C512" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D512" t="n">
         <v>340</v>
@@ -8636,7 +8636,7 @@
         <v>2</v>
       </c>
       <c r="C513" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D513" t="n">
         <v>10</v>
@@ -8652,7 +8652,7 @@
         <v>2</v>
       </c>
       <c r="C514" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D514" t="n">
         <v>5</v>
@@ -8668,7 +8668,7 @@
         <v>2</v>
       </c>
       <c r="C515" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D515" t="n">
         <v>7</v>
@@ -8684,7 +8684,7 @@
         <v>2</v>
       </c>
       <c r="C516" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D516" t="n">
         <v>10</v>
@@ -8700,7 +8700,7 @@
         <v>2</v>
       </c>
       <c r="C517" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D517" t="n">
         <v>20</v>
@@ -8716,7 +8716,7 @@
         <v>2</v>
       </c>
       <c r="C518" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D518" t="n">
         <v>45</v>
@@ -8732,7 +8732,7 @@
         <v>3</v>
       </c>
       <c r="C519" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D519" t="n">
         <v>454</v>
@@ -8748,7 +8748,7 @@
         <v>3</v>
       </c>
       <c r="C520" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D520" t="n">
         <v>281</v>
@@ -8764,7 +8764,7 @@
         <v>3</v>
       </c>
       <c r="C521" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D521" t="n">
         <v>14</v>
@@ -8780,7 +8780,7 @@
         <v>4</v>
       </c>
       <c r="C522" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D522" t="n">
         <v>244</v>
@@ -8796,7 +8796,7 @@
         <v>4</v>
       </c>
       <c r="C523" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D523" t="n">
         <v>11</v>
@@ -8812,7 +8812,7 @@
         <v>4</v>
       </c>
       <c r="C524" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D524" t="n">
         <v>23</v>
@@ -8828,7 +8828,7 @@
         <v>4</v>
       </c>
       <c r="C525" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D525" t="n">
         <v>10</v>
@@ -8844,7 +8844,7 @@
         <v>4</v>
       </c>
       <c r="C526" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D526" t="n">
         <v>6</v>
@@ -8860,7 +8860,7 @@
         <v>4</v>
       </c>
       <c r="C527" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D527" t="n">
         <v>5</v>
@@ -8876,7 +8876,7 @@
         <v>4</v>
       </c>
       <c r="C528" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D528" t="n">
         <v>143</v>
@@ -8892,7 +8892,7 @@
         <v>5</v>
       </c>
       <c r="C529" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D529" t="n">
         <v>6</v>
@@ -8908,7 +8908,7 @@
         <v>5</v>
       </c>
       <c r="C530" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D530" t="n">
         <v>26</v>
@@ -8924,7 +8924,7 @@
         <v>5</v>
       </c>
       <c r="C531" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D531" t="n">
         <v>8</v>
@@ -8940,7 +8940,7 @@
         <v>5</v>
       </c>
       <c r="C532" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D532" t="n">
         <v>51</v>
@@ -8956,7 +8956,7 @@
         <v>5</v>
       </c>
       <c r="C533" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D533" t="n">
         <v>15</v>
@@ -8972,7 +8972,7 @@
         <v>5</v>
       </c>
       <c r="C534" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D534" t="n">
         <v>13</v>
@@ -8988,7 +8988,7 @@
         <v>5</v>
       </c>
       <c r="C535" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D535" t="n">
         <v>11</v>
@@ -9004,7 +9004,7 @@
         <v>6</v>
       </c>
       <c r="C536" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D536" t="n">
         <v>48</v>
@@ -9020,7 +9020,7 @@
         <v>6</v>
       </c>
       <c r="C537" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D537" t="n">
         <v>944</v>
@@ -9036,7 +9036,7 @@
         <v>6</v>
       </c>
       <c r="C538" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D538" t="n">
         <v>25</v>
@@ -9052,7 +9052,7 @@
         <v>1</v>
       </c>
       <c r="C539" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D539" t="n">
         <v>894</v>
@@ -9068,7 +9068,7 @@
         <v>1</v>
       </c>
       <c r="C540" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D540" t="n">
         <v>7</v>
@@ -9084,7 +9084,7 @@
         <v>1</v>
       </c>
       <c r="C541" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D541" t="n">
         <v>23</v>
@@ -9100,7 +9100,7 @@
         <v>2</v>
       </c>
       <c r="C542" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D542" t="n">
         <v>56</v>
@@ -9116,7 +9116,7 @@
         <v>2</v>
       </c>
       <c r="C543" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D543" t="n">
         <v>12</v>
@@ -9132,7 +9132,7 @@
         <v>3</v>
       </c>
       <c r="C544" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D544" t="n">
         <v>10</v>
@@ -9148,7 +9148,7 @@
         <v>3</v>
       </c>
       <c r="C545" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D545" t="n">
         <v>5</v>
@@ -9164,7 +9164,7 @@
         <v>3</v>
       </c>
       <c r="C546" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D546" t="n">
         <v>8</v>
@@ -9180,7 +9180,7 @@
         <v>3</v>
       </c>
       <c r="C547" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D547" t="n">
         <v>50</v>
@@ -9196,7 +9196,7 @@
         <v>3</v>
       </c>
       <c r="C548" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D548" t="n">
         <v>19</v>
@@ -9212,7 +9212,7 @@
         <v>3</v>
       </c>
       <c r="C549" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D549" t="n">
         <v>7</v>
@@ -9228,7 +9228,7 @@
         <v>3</v>
       </c>
       <c r="C550" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D550" t="n">
         <v>7</v>
@@ -9244,7 +9244,7 @@
         <v>3</v>
       </c>
       <c r="C551" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D551" t="n">
         <v>117</v>
@@ -9260,7 +9260,7 @@
         <v>3</v>
       </c>
       <c r="C552" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D552" t="n">
         <v>6</v>
@@ -9276,7 +9276,7 @@
         <v>3</v>
       </c>
       <c r="C553" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D553" t="n">
         <v>37</v>
@@ -9292,7 +9292,7 @@
         <v>3</v>
       </c>
       <c r="C554" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D554" t="n">
         <v>28</v>
@@ -9308,7 +9308,7 @@
         <v>4</v>
       </c>
       <c r="C555" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D555" t="n">
         <v>9</v>
@@ -9324,7 +9324,7 @@
         <v>4</v>
       </c>
       <c r="C556" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D556" t="n">
         <v>168</v>
@@ -9340,7 +9340,7 @@
         <v>4</v>
       </c>
       <c r="C557" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D557" t="n">
         <v>63</v>
@@ -9356,7 +9356,7 @@
         <v>4</v>
       </c>
       <c r="C558" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D558" t="n">
         <v>96</v>
@@ -9372,7 +9372,7 @@
         <v>4</v>
       </c>
       <c r="C559" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D559" t="n">
         <v>179</v>
@@ -9388,7 +9388,7 @@
         <v>4</v>
       </c>
       <c r="C560" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D560" t="n">
         <v>74</v>
@@ -9404,7 +9404,7 @@
         <v>4</v>
       </c>
       <c r="C561" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D561" t="n">
         <v>5</v>
@@ -9420,7 +9420,7 @@
         <v>1</v>
       </c>
       <c r="C562" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D562" t="n">
         <v>1331</v>
@@ -9436,7 +9436,7 @@
         <v>1</v>
       </c>
       <c r="C563" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D563" t="n">
         <v>60</v>
@@ -9452,7 +9452,7 @@
         <v>2</v>
       </c>
       <c r="C564" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D564" t="n">
         <v>28</v>
@@ -9468,7 +9468,7 @@
         <v>2</v>
       </c>
       <c r="C565" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D565" t="n">
         <v>63</v>
@@ -9484,7 +9484,7 @@
         <v>2</v>
       </c>
       <c r="C566" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D566" t="n">
         <v>20</v>
@@ -9500,7 +9500,7 @@
         <v>2</v>
       </c>
       <c r="C567" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D567" t="n">
         <v>131</v>
@@ -9516,7 +9516,7 @@
         <v>2</v>
       </c>
       <c r="C568" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D568" t="n">
         <v>15</v>
@@ -9532,7 +9532,7 @@
         <v>2</v>
       </c>
       <c r="C569" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D569" t="n">
         <v>5</v>
@@ -9548,7 +9548,7 @@
         <v>2</v>
       </c>
       <c r="C570" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D570" t="n">
         <v>37</v>
@@ -9564,7 +9564,7 @@
         <v>2</v>
       </c>
       <c r="C571" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D571" t="n">
         <v>56</v>
@@ -9580,7 +9580,7 @@
         <v>2</v>
       </c>
       <c r="C572" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D572" t="n">
         <v>116</v>
@@ -9596,7 +9596,7 @@
         <v>2</v>
       </c>
       <c r="C573" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D573" t="n">
         <v>21</v>
@@ -9612,7 +9612,7 @@
         <v>2</v>
       </c>
       <c r="C574" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D574" t="n">
         <v>25</v>
@@ -9628,7 +9628,7 @@
         <v>2</v>
       </c>
       <c r="C575" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D575" t="n">
         <v>7</v>
@@ -9644,7 +9644,7 @@
         <v>2</v>
       </c>
       <c r="C576" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D576" t="n">
         <v>25</v>
@@ -9660,7 +9660,7 @@
         <v>3</v>
       </c>
       <c r="C577" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D577" t="n">
         <v>572</v>
@@ -9676,7 +9676,7 @@
         <v>3</v>
       </c>
       <c r="C578" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D578" t="n">
         <v>70</v>
@@ -9692,7 +9692,7 @@
         <v>3</v>
       </c>
       <c r="C579" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D579" t="n">
         <v>36</v>
@@ -9708,7 +9708,7 @@
         <v>3</v>
       </c>
       <c r="C580" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D580" t="n">
         <v>123</v>
@@ -9724,7 +9724,7 @@
         <v>3</v>
       </c>
       <c r="C581" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D581" t="n">
         <v>188</v>
@@ -9740,7 +9740,7 @@
         <v>4</v>
       </c>
       <c r="C582" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D582" t="n">
         <v>45</v>
@@ -9756,7 +9756,7 @@
         <v>4</v>
       </c>
       <c r="C583" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D583" t="n">
         <v>496</v>
@@ -9772,7 +9772,7 @@
         <v>4</v>
       </c>
       <c r="C584" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D584" t="n">
         <v>21</v>
@@ -9788,7 +9788,7 @@
         <v>5</v>
       </c>
       <c r="C585" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D585" t="n">
         <v>11</v>
@@ -9804,7 +9804,7 @@
         <v>5</v>
       </c>
       <c r="C586" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D586" t="n">
         <v>80</v>
@@ -9820,7 +9820,7 @@
         <v>5</v>
       </c>
       <c r="C587" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D587" t="n">
         <v>6</v>
@@ -9836,7 +9836,7 @@
         <v>5</v>
       </c>
       <c r="C588" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D588" t="n">
         <v>87</v>
@@ -9852,7 +9852,7 @@
         <v>5</v>
       </c>
       <c r="C589" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D589" t="n">
         <v>49</v>
@@ -9868,7 +9868,7 @@
         <v>5</v>
       </c>
       <c r="C590" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D590" t="n">
         <v>54</v>
@@ -9884,7 +9884,7 @@
         <v>5</v>
       </c>
       <c r="C591" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D591" t="n">
         <v>38</v>
@@ -9900,7 +9900,7 @@
         <v>5</v>
       </c>
       <c r="C592" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D592" t="n">
         <v>25</v>
@@ -9916,7 +9916,7 @@
         <v>5</v>
       </c>
       <c r="C593" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D593" t="n">
         <v>148</v>
@@ -9932,7 +9932,7 @@
         <v>6</v>
       </c>
       <c r="C594" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D594" t="n">
         <v>128</v>
@@ -9948,7 +9948,7 @@
         <v>6</v>
       </c>
       <c r="C595" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D595" t="n">
         <v>31</v>
@@ -9964,7 +9964,7 @@
         <v>7</v>
       </c>
       <c r="C596" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D596" t="n">
         <v>61</v>
@@ -9980,7 +9980,7 @@
         <v>7</v>
       </c>
       <c r="C597" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D597" t="n">
         <v>331</v>
@@ -9996,7 +9996,7 @@
         <v>7</v>
       </c>
       <c r="C598" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D598" t="n">
         <v>24</v>
@@ -10012,7 +10012,7 @@
         <v>7</v>
       </c>
       <c r="C599" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D599" t="n">
         <v>26</v>
@@ -10028,7 +10028,7 @@
         <v>7</v>
       </c>
       <c r="C600" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D600" t="n">
         <v>127</v>
@@ -10044,7 +10044,7 @@
         <v>7</v>
       </c>
       <c r="C601" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D601" t="n">
         <v>37</v>
@@ -10060,7 +10060,7 @@
         <v>7</v>
       </c>
       <c r="C602" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D602" t="n">
         <v>120</v>
@@ -10076,7 +10076,7 @@
         <v>7</v>
       </c>
       <c r="C603" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D603" t="n">
         <v>78</v>
@@ -10092,7 +10092,7 @@
         <v>8</v>
       </c>
       <c r="C604" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D604" t="n">
         <v>295</v>
@@ -10108,7 +10108,7 @@
         <v>8</v>
       </c>
       <c r="C605" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D605" t="n">
         <v>94</v>
@@ -10124,7 +10124,7 @@
         <v>8</v>
       </c>
       <c r="C606" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D606" t="n">
         <v>7</v>
@@ -10140,7 +10140,7 @@
         <v>10</v>
       </c>
       <c r="C607" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D607" t="n">
         <v>16</v>
@@ -10156,7 +10156,7 @@
         <v>10</v>
       </c>
       <c r="C608" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D608" t="n">
         <v>15</v>
@@ -10172,7 +10172,7 @@
         <v>10</v>
       </c>
       <c r="C609" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D609" t="n">
         <v>6</v>
@@ -10188,7 +10188,7 @@
         <v>10</v>
       </c>
       <c r="C610" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D610" t="n">
         <v>9</v>
@@ -10204,7 +10204,7 @@
         <v>10</v>
       </c>
       <c r="C611" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D611" t="n">
         <v>31</v>
@@ -10220,7 +10220,7 @@
         <v>10</v>
       </c>
       <c r="C612" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D612" t="n">
         <v>26</v>
@@ -10236,7 +10236,7 @@
         <v>10</v>
       </c>
       <c r="C613" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D613" t="n">
         <v>17</v>
@@ -10252,7 +10252,7 @@
         <v>10</v>
       </c>
       <c r="C614" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D614" t="n">
         <v>16</v>
@@ -10268,7 +10268,7 @@
         <v>10</v>
       </c>
       <c r="C615" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D615" t="n">
         <v>67</v>
@@ -10284,7 +10284,7 @@
         <v>10</v>
       </c>
       <c r="C616" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D616" t="n">
         <v>6</v>
@@ -10300,7 +10300,7 @@
         <v>10</v>
       </c>
       <c r="C617" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D617" t="n">
         <v>91</v>
@@ -10316,7 +10316,7 @@
         <v>10</v>
       </c>
       <c r="C618" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D618" t="n">
         <v>34</v>
@@ -10332,7 +10332,7 @@
         <v>10</v>
       </c>
       <c r="C619" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D619" t="n">
         <v>26</v>
@@ -10348,7 +10348,7 @@
         <v>1</v>
       </c>
       <c r="C620" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D620" t="n">
         <v>21</v>
@@ -10364,7 +10364,7 @@
         <v>1</v>
       </c>
       <c r="C621" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D621" t="n">
         <v>8</v>
@@ -10380,7 +10380,7 @@
         <v>1</v>
       </c>
       <c r="C622" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D622" t="n">
         <v>35</v>
@@ -10396,7 +10396,7 @@
         <v>1</v>
       </c>
       <c r="C623" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D623" t="n">
         <v>84</v>
@@ -10412,7 +10412,7 @@
         <v>1</v>
       </c>
       <c r="C624" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D624" t="n">
         <v>12</v>
@@ -10428,7 +10428,7 @@
         <v>1</v>
       </c>
       <c r="C625" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D625" t="n">
         <v>24</v>
@@ -10444,7 +10444,7 @@
         <v>1</v>
       </c>
       <c r="C626" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D626" t="n">
         <v>36</v>
@@ -10460,7 +10460,7 @@
         <v>1</v>
       </c>
       <c r="C627" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D627" t="n">
         <v>202</v>
@@ -10476,7 +10476,7 @@
         <v>1</v>
       </c>
       <c r="C628" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D628" t="n">
         <v>15</v>
@@ -10492,7 +10492,7 @@
         <v>1</v>
       </c>
       <c r="C629" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D629" t="n">
         <v>9</v>
@@ -10508,7 +10508,7 @@
         <v>2</v>
       </c>
       <c r="C630" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D630" t="n">
         <v>776</v>
@@ -10524,7 +10524,7 @@
         <v>2</v>
       </c>
       <c r="C631" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D631" t="n">
         <v>5</v>
@@ -10540,7 +10540,7 @@
         <v>2</v>
       </c>
       <c r="C632" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D632" t="n">
         <v>12</v>
@@ -10556,7 +10556,7 @@
         <v>2</v>
       </c>
       <c r="C633" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D633" t="n">
         <v>199</v>
@@ -10572,7 +10572,7 @@
         <v>2</v>
       </c>
       <c r="C634" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D634" t="n">
         <v>20</v>
@@ -10588,7 +10588,7 @@
         <v>2</v>
       </c>
       <c r="C635" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D635" t="n">
         <v>8</v>
@@ -10604,7 +10604,7 @@
         <v>2</v>
       </c>
       <c r="C636" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D636" t="n">
         <v>9</v>
@@ -10620,7 +10620,7 @@
         <v>2</v>
       </c>
       <c r="C637" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D637" t="n">
         <v>54</v>
@@ -10636,7 +10636,7 @@
         <v>2</v>
       </c>
       <c r="C638" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D638" t="n">
         <v>24</v>
@@ -10652,7 +10652,7 @@
         <v>3</v>
       </c>
       <c r="C639" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D639" t="n">
         <v>6</v>
@@ -10668,7 +10668,7 @@
         <v>3</v>
       </c>
       <c r="C640" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D640" t="n">
         <v>18</v>
@@ -10684,7 +10684,7 @@
         <v>3</v>
       </c>
       <c r="C641" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D641" t="n">
         <v>6</v>
@@ -10700,7 +10700,7 @@
         <v>3</v>
       </c>
       <c r="C642" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D642" t="n">
         <v>98</v>
@@ -10716,7 +10716,7 @@
         <v>3</v>
       </c>
       <c r="C643" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D643" t="n">
         <v>229</v>
@@ -10732,7 +10732,7 @@
         <v>3</v>
       </c>
       <c r="C644" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D644" t="n">
         <v>60</v>
@@ -10748,7 +10748,7 @@
         <v>3</v>
       </c>
       <c r="C645" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D645" t="n">
         <v>12</v>
@@ -10764,7 +10764,7 @@
         <v>4</v>
       </c>
       <c r="C646" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D646" t="n">
         <v>98</v>
@@ -10780,7 +10780,7 @@
         <v>4</v>
       </c>
       <c r="C647" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D647" t="n">
         <v>10</v>
@@ -10796,7 +10796,7 @@
         <v>4</v>
       </c>
       <c r="C648" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D648" t="n">
         <v>16</v>
@@ -10812,7 +10812,7 @@
         <v>4</v>
       </c>
       <c r="C649" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D649" t="n">
         <v>422</v>
@@ -10828,7 +10828,7 @@
         <v>4</v>
       </c>
       <c r="C650" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D650" t="n">
         <v>14</v>
@@ -10844,7 +10844,7 @@
         <v>4</v>
       </c>
       <c r="C651" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D651" t="n">
         <v>23</v>
@@ -10860,7 +10860,7 @@
         <v>4</v>
       </c>
       <c r="C652" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D652" t="n">
         <v>31</v>
@@ -10876,7 +10876,7 @@
         <v>5</v>
       </c>
       <c r="C653" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D653" t="n">
         <v>55</v>
@@ -10892,7 +10892,7 @@
         <v>5</v>
       </c>
       <c r="C654" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D654" t="n">
         <v>316</v>
@@ -10908,7 +10908,7 @@
         <v>5</v>
       </c>
       <c r="C655" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D655" t="n">
         <v>116</v>
@@ -10924,7 +10924,7 @@
         <v>5</v>
       </c>
       <c r="C656" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D656" t="n">
         <v>11</v>
@@ -10940,7 +10940,7 @@
         <v>5</v>
       </c>
       <c r="C657" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D657" t="n">
         <v>93</v>
@@ -10956,7 +10956,7 @@
         <v>6</v>
       </c>
       <c r="C658" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D658" t="n">
         <v>23</v>
@@ -10972,7 +10972,7 @@
         <v>6</v>
       </c>
       <c r="C659" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D659" t="n">
         <v>8</v>
@@ -10988,7 +10988,7 @@
         <v>6</v>
       </c>
       <c r="C660" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D660" t="n">
         <v>28</v>
@@ -11004,7 +11004,7 @@
         <v>6</v>
       </c>
       <c r="C661" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D661" t="n">
         <v>21</v>
@@ -11020,7 +11020,7 @@
         <v>6</v>
       </c>
       <c r="C662" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D662" t="n">
         <v>605</v>
@@ -11036,7 +11036,7 @@
         <v>6</v>
       </c>
       <c r="C663" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D663" t="n">
         <v>7</v>
@@ -11052,7 +11052,7 @@
         <v>6</v>
       </c>
       <c r="C664" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D664" t="n">
         <v>8</v>
@@ -11068,7 +11068,7 @@
         <v>6</v>
       </c>
       <c r="C665" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D665" t="n">
         <v>8</v>
@@ -11084,7 +11084,7 @@
         <v>7</v>
       </c>
       <c r="C666" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D666" t="n">
         <v>30</v>
@@ -11100,7 +11100,7 @@
         <v>7</v>
       </c>
       <c r="C667" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D667" t="n">
         <v>14</v>
@@ -11116,7 +11116,7 @@
         <v>7</v>
       </c>
       <c r="C668" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D668" t="n">
         <v>476</v>
@@ -11132,7 +11132,7 @@
         <v>8</v>
       </c>
       <c r="C669" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D669" t="n">
         <v>17</v>
@@ -11148,7 +11148,7 @@
         <v>8</v>
       </c>
       <c r="C670" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D670" t="n">
         <v>15</v>
@@ -11164,7 +11164,7 @@
         <v>8</v>
       </c>
       <c r="C671" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D671" t="n">
         <v>21</v>
@@ -11180,7 +11180,7 @@
         <v>8</v>
       </c>
       <c r="C672" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D672" t="n">
         <v>13</v>
@@ -11196,7 +11196,7 @@
         <v>8</v>
       </c>
       <c r="C673" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D673" t="n">
         <v>25</v>
@@ -11212,7 +11212,7 @@
         <v>1</v>
       </c>
       <c r="C674" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D674" t="n">
         <v>22</v>
@@ -11228,7 +11228,7 @@
         <v>1</v>
       </c>
       <c r="C675" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D675" t="n">
         <v>222</v>
@@ -11244,7 +11244,7 @@
         <v>1</v>
       </c>
       <c r="C676" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D676" t="n">
         <v>36</v>
@@ -11260,7 +11260,7 @@
         <v>1</v>
       </c>
       <c r="C677" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D677" t="n">
         <v>11</v>
@@ -11276,7 +11276,7 @@
         <v>1</v>
       </c>
       <c r="C678" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D678" t="n">
         <v>44</v>
@@ -11292,7 +11292,7 @@
         <v>2</v>
       </c>
       <c r="C679" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D679" t="n">
         <v>243</v>
@@ -11308,7 +11308,7 @@
         <v>2</v>
       </c>
       <c r="C680" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D680" t="n">
         <v>6</v>
@@ -11324,7 +11324,7 @@
         <v>2</v>
       </c>
       <c r="C681" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D681" t="n">
         <v>10</v>
@@ -11340,7 +11340,7 @@
         <v>2</v>
       </c>
       <c r="C682" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D682" t="n">
         <v>5</v>
@@ -11356,7 +11356,7 @@
         <v>2</v>
       </c>
       <c r="C683" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D683" t="n">
         <v>14</v>
@@ -11372,7 +11372,7 @@
         <v>2</v>
       </c>
       <c r="C684" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D684" t="n">
         <v>13</v>
@@ -11388,7 +11388,7 @@
         <v>2</v>
       </c>
       <c r="C685" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D685" t="n">
         <v>196</v>
@@ -11404,7 +11404,7 @@
         <v>2</v>
       </c>
       <c r="C686" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D686" t="n">
         <v>8</v>
@@ -11420,7 +11420,7 @@
         <v>2</v>
       </c>
       <c r="C687" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D687" t="n">
         <v>89</v>
@@ -11436,7 +11436,7 @@
         <v>2</v>
       </c>
       <c r="C688" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D688" t="n">
         <v>30</v>
@@ -11452,7 +11452,7 @@
         <v>2</v>
       </c>
       <c r="C689" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D689" t="n">
         <v>22</v>
@@ -11468,7 +11468,7 @@
         <v>2</v>
       </c>
       <c r="C690" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D690" t="n">
         <v>20</v>
@@ -11484,7 +11484,7 @@
         <v>3</v>
       </c>
       <c r="C691" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D691" t="n">
         <v>992</v>
@@ -11500,7 +11500,7 @@
         <v>4</v>
       </c>
       <c r="C692" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D692" t="n">
         <v>19</v>
@@ -11516,7 +11516,7 @@
         <v>4</v>
       </c>
       <c r="C693" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D693" t="n">
         <v>5</v>
@@ -11532,7 +11532,7 @@
         <v>4</v>
       </c>
       <c r="C694" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D694" t="n">
         <v>13</v>
@@ -11548,7 +11548,7 @@
         <v>4</v>
       </c>
       <c r="C695" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D695" t="n">
         <v>33</v>
@@ -11564,7 +11564,7 @@
         <v>4</v>
       </c>
       <c r="C696" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D696" t="n">
         <v>68</v>
@@ -11580,7 +11580,7 @@
         <v>4</v>
       </c>
       <c r="C697" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D697" t="n">
         <v>57</v>
@@ -11596,7 +11596,7 @@
         <v>4</v>
       </c>
       <c r="C698" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D698" t="n">
         <v>18</v>
@@ -11612,7 +11612,7 @@
         <v>4</v>
       </c>
       <c r="C699" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D699" t="n">
         <v>316</v>
@@ -11628,7 +11628,7 @@
         <v>6</v>
       </c>
       <c r="C700" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D700" t="n">
         <v>12</v>
@@ -11644,7 +11644,7 @@
         <v>6</v>
       </c>
       <c r="C701" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D701" t="n">
         <v>61</v>
@@ -11660,7 +11660,7 @@
         <v>6</v>
       </c>
       <c r="C702" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D702" t="n">
         <v>345</v>
@@ -11676,7 +11676,7 @@
         <v>6</v>
       </c>
       <c r="C703" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D703" t="n">
         <v>62</v>
@@ -11692,7 +11692,7 @@
         <v>7</v>
       </c>
       <c r="C704" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D704" t="n">
         <v>71</v>
@@ -11708,7 +11708,7 @@
         <v>7</v>
       </c>
       <c r="C705" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D705" t="n">
         <v>834</v>
@@ -11724,7 +11724,7 @@
         <v>7</v>
       </c>
       <c r="C706" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D706" t="n">
         <v>5</v>
@@ -11740,7 +11740,7 @@
         <v>7</v>
       </c>
       <c r="C707" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D707" t="n">
         <v>46</v>
@@ -11756,7 +11756,7 @@
         <v>7</v>
       </c>
       <c r="C708" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D708" t="n">
         <v>91</v>
@@ -11772,7 +11772,7 @@
         <v>8</v>
       </c>
       <c r="C709" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D709" t="n">
         <v>12</v>
@@ -11788,7 +11788,7 @@
         <v>8</v>
       </c>
       <c r="C710" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D710" t="n">
         <v>13</v>
@@ -11804,7 +11804,7 @@
         <v>8</v>
       </c>
       <c r="C711" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D711" t="n">
         <v>11</v>
@@ -11820,7 +11820,7 @@
         <v>8</v>
       </c>
       <c r="C712" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D712" t="n">
         <v>24</v>
@@ -11836,7 +11836,7 @@
         <v>8</v>
       </c>
       <c r="C713" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D713" t="n">
         <v>18</v>
@@ -11852,7 +11852,7 @@
         <v>8</v>
       </c>
       <c r="C714" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D714" t="n">
         <v>16</v>
@@ -11868,7 +11868,7 @@
         <v>8</v>
       </c>
       <c r="C715" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D715" t="n">
         <v>8</v>
@@ -11884,7 +11884,7 @@
         <v>8</v>
       </c>
       <c r="C716" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D716" t="n">
         <v>33</v>
@@ -11900,7 +11900,7 @@
         <v>8</v>
       </c>
       <c r="C717" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D717" t="n">
         <v>153</v>
@@ -11916,7 +11916,7 @@
         <v>8</v>
       </c>
       <c r="C718" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D718" t="n">
         <v>8</v>
@@ -11932,7 +11932,7 @@
         <v>8</v>
       </c>
       <c r="C719" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D719" t="n">
         <v>6</v>
@@ -11948,7 +11948,7 @@
         <v>9</v>
       </c>
       <c r="C720" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D720" t="n">
         <v>29</v>
@@ -11964,7 +11964,7 @@
         <v>9</v>
       </c>
       <c r="C721" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D721" t="n">
         <v>27</v>
@@ -11980,7 +11980,7 @@
         <v>9</v>
       </c>
       <c r="C722" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D722" t="n">
         <v>22</v>
@@ -11996,7 +11996,7 @@
         <v>9</v>
       </c>
       <c r="C723" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D723" t="n">
         <v>23</v>
@@ -12012,7 +12012,7 @@
         <v>9</v>
       </c>
       <c r="C724" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D724" t="n">
         <v>117</v>
@@ -12028,7 +12028,7 @@
         <v>9</v>
       </c>
       <c r="C725" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D725" t="n">
         <v>68</v>
@@ -12044,7 +12044,7 @@
         <v>9</v>
       </c>
       <c r="C726" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D726" t="n">
         <v>5</v>
@@ -12060,7 +12060,7 @@
         <v>9</v>
       </c>
       <c r="C727" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D727" t="n">
         <v>5</v>
@@ -12076,7 +12076,7 @@
         <v>11</v>
       </c>
       <c r="C728" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D728" t="n">
         <v>14</v>
@@ -12092,7 +12092,7 @@
         <v>11</v>
       </c>
       <c r="C729" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D729" t="n">
         <v>152</v>
@@ -12108,7 +12108,7 @@
         <v>11</v>
       </c>
       <c r="C730" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D730" t="n">
         <v>32</v>
@@ -12124,7 +12124,7 @@
         <v>11</v>
       </c>
       <c r="C731" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D731" t="n">
         <v>41</v>
@@ -12140,7 +12140,7 @@
         <v>11</v>
       </c>
       <c r="C732" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D732" t="n">
         <v>20</v>
@@ -12156,7 +12156,7 @@
         <v>11</v>
       </c>
       <c r="C733" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D733" t="n">
         <v>7</v>
@@ -12172,7 +12172,7 @@
         <v>11</v>
       </c>
       <c r="C734" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D734" t="n">
         <v>15</v>
@@ -12188,7 +12188,7 @@
         <v>11</v>
       </c>
       <c r="C735" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D735" t="n">
         <v>34</v>
@@ -12204,7 +12204,7 @@
         <v>11</v>
       </c>
       <c r="C736" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D736" t="n">
         <v>5</v>
@@ -12220,7 +12220,7 @@
         <v>11</v>
       </c>
       <c r="C737" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D737" t="n">
         <v>20</v>
@@ -12236,7 +12236,7 @@
         <v>11</v>
       </c>
       <c r="C738" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D738" t="n">
         <v>121</v>
@@ -12252,7 +12252,7 @@
         <v>11</v>
       </c>
       <c r="C739" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D739" t="n">
         <v>23</v>
@@ -12268,7 +12268,7 @@
         <v>11</v>
       </c>
       <c r="C740" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D740" t="n">
         <v>19</v>
@@ -12284,7 +12284,7 @@
         <v>11</v>
       </c>
       <c r="C741" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D741" t="n">
         <v>12</v>
@@ -12300,7 +12300,7 @@
         <v>11</v>
       </c>
       <c r="C742" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D742" t="n">
         <v>17</v>
@@ -12316,7 +12316,7 @@
         <v>11</v>
       </c>
       <c r="C743" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D743" t="n">
         <v>31</v>
@@ -12332,7 +12332,7 @@
         <v>11</v>
       </c>
       <c r="C744" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D744" t="n">
         <v>47</v>
@@ -12348,7 +12348,7 @@
         <v>11</v>
       </c>
       <c r="C745" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D745" t="n">
         <v>40</v>
@@ -12364,7 +12364,7 @@
         <v>12</v>
       </c>
       <c r="C746" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D746" t="n">
         <v>43</v>
@@ -12380,7 +12380,7 @@
         <v>12</v>
       </c>
       <c r="C747" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D747" t="n">
         <v>871</v>
@@ -12396,7 +12396,7 @@
         <v>13</v>
       </c>
       <c r="C748" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D748" t="n">
         <v>985</v>
@@ -12412,7 +12412,7 @@
         <v>13</v>
       </c>
       <c r="C749" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D749" t="n">
         <v>17</v>
@@ -12428,7 +12428,7 @@
         <v>13</v>
       </c>
       <c r="C750" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D750" t="n">
         <v>63</v>
@@ -12444,7 +12444,7 @@
         <v>13</v>
       </c>
       <c r="C751" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D751" t="n">
         <v>9</v>
@@ -12460,7 +12460,7 @@
         <v>13</v>
       </c>
       <c r="C752" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D752" t="n">
         <v>15</v>
@@ -12476,7 +12476,7 @@
         <v>14</v>
       </c>
       <c r="C753" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D753" t="n">
         <v>18</v>
@@ -12492,7 +12492,7 @@
         <v>14</v>
       </c>
       <c r="C754" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D754" t="n">
         <v>13</v>
@@ -12508,7 +12508,7 @@
         <v>14</v>
       </c>
       <c r="C755" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D755" t="n">
         <v>185</v>
@@ -12524,7 +12524,7 @@
         <v>14</v>
       </c>
       <c r="C756" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D756" t="n">
         <v>28</v>
@@ -12540,7 +12540,7 @@
         <v>14</v>
       </c>
       <c r="C757" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D757" t="n">
         <v>9</v>
@@ -12556,7 +12556,7 @@
         <v>14</v>
       </c>
       <c r="C758" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D758" t="n">
         <v>20</v>
@@ -12572,7 +12572,7 @@
         <v>14</v>
       </c>
       <c r="C759" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D759" t="n">
         <v>21</v>
@@ -12588,7 +12588,7 @@
         <v>14</v>
       </c>
       <c r="C760" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D760" t="n">
         <v>42</v>
@@ -12604,7 +12604,7 @@
         <v>14</v>
       </c>
       <c r="C761" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D761" t="n">
         <v>35</v>
@@ -12620,7 +12620,7 @@
         <v>15</v>
       </c>
       <c r="C762" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D762" t="n">
         <v>5</v>
@@ -12636,7 +12636,7 @@
         <v>15</v>
       </c>
       <c r="C763" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D763" t="n">
         <v>9</v>
@@ -12652,7 +12652,7 @@
         <v>15</v>
       </c>
       <c r="C764" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D764" t="n">
         <v>8</v>
@@ -12668,7 +12668,7 @@
         <v>15</v>
       </c>
       <c r="C765" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D765" t="n">
         <v>13</v>
@@ -12684,7 +12684,7 @@
         <v>15</v>
       </c>
       <c r="C766" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D766" t="n">
         <v>244</v>
@@ -12700,7 +12700,7 @@
         <v>15</v>
       </c>
       <c r="C767" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D767" t="n">
         <v>30</v>
@@ -12716,7 +12716,7 @@
         <v>1</v>
       </c>
       <c r="C768" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D768" t="n">
         <v>9</v>
@@ -12732,7 +12732,7 @@
         <v>1</v>
       </c>
       <c r="C769" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D769" t="n">
         <v>22</v>
@@ -12748,7 +12748,7 @@
         <v>1</v>
       </c>
       <c r="C770" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D770" t="n">
         <v>48</v>
@@ -12764,7 +12764,7 @@
         <v>1</v>
       </c>
       <c r="C771" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D771" t="n">
         <v>25</v>
@@ -12780,7 +12780,7 @@
         <v>1</v>
       </c>
       <c r="C772" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D772" t="n">
         <v>340</v>
@@ -12796,7 +12796,7 @@
         <v>1</v>
       </c>
       <c r="C773" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D773" t="n">
         <v>96</v>
@@ -12812,7 +12812,7 @@
         <v>1</v>
       </c>
       <c r="C774" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D774" t="n">
         <v>56</v>
@@ -12828,7 +12828,7 @@
         <v>1</v>
       </c>
       <c r="C775" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D775" t="n">
         <v>7</v>
@@ -12844,7 +12844,7 @@
         <v>2</v>
       </c>
       <c r="C776" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D776" t="n">
         <v>112</v>
@@ -12860,7 +12860,7 @@
         <v>2</v>
       </c>
       <c r="C777" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D777" t="n">
         <v>17</v>
@@ -12876,7 +12876,7 @@
         <v>2</v>
       </c>
       <c r="C778" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D778" t="n">
         <v>13</v>
@@ -12892,7 +12892,7 @@
         <v>2</v>
       </c>
       <c r="C779" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D779" t="n">
         <v>62</v>
@@ -12908,7 +12908,7 @@
         <v>2</v>
       </c>
       <c r="C780" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D780" t="n">
         <v>42</v>
@@ -12924,7 +12924,7 @@
         <v>2</v>
       </c>
       <c r="C781" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D781" t="n">
         <v>196</v>
@@ -12940,7 +12940,7 @@
         <v>2</v>
       </c>
       <c r="C782" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D782" t="n">
         <v>16</v>
@@ -12956,7 +12956,7 @@
         <v>2</v>
       </c>
       <c r="C783" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D783" t="n">
         <v>36</v>
@@ -12972,7 +12972,7 @@
         <v>2</v>
       </c>
       <c r="C784" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D784" t="n">
         <v>11</v>
@@ -12988,7 +12988,7 @@
         <v>2</v>
       </c>
       <c r="C785" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D785" t="n">
         <v>325</v>
@@ -13004,7 +13004,7 @@
         <v>2</v>
       </c>
       <c r="C786" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D786" t="n">
         <v>13</v>
@@ -13020,7 +13020,7 @@
         <v>3</v>
       </c>
       <c r="C787" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D787" t="n">
         <v>8</v>
@@ -13036,7 +13036,7 @@
         <v>3</v>
       </c>
       <c r="C788" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D788" t="n">
         <v>16</v>
@@ -13052,7 +13052,7 @@
         <v>3</v>
       </c>
       <c r="C789" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D789" t="n">
         <v>5</v>
@@ -13068,7 +13068,7 @@
         <v>3</v>
       </c>
       <c r="C790" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D790" t="n">
         <v>339</v>
@@ -13084,7 +13084,7 @@
         <v>3</v>
       </c>
       <c r="C791" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D791" t="n">
         <v>150</v>
@@ -13100,7 +13100,7 @@
         <v>3</v>
       </c>
       <c r="C792" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D792" t="n">
         <v>13</v>
@@ -13116,7 +13116,7 @@
         <v>3</v>
       </c>
       <c r="C793" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D793" t="n">
         <v>44</v>
@@ -13132,7 +13132,7 @@
         <v>4</v>
       </c>
       <c r="C794" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D794" t="n">
         <v>421</v>
@@ -13148,7 +13148,7 @@
         <v>4</v>
       </c>
       <c r="C795" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D795" t="n">
         <v>94</v>
@@ -13164,7 +13164,7 @@
         <v>4</v>
       </c>
       <c r="C796" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D796" t="n">
         <v>48</v>
@@ -13180,7 +13180,7 @@
         <v>4</v>
       </c>
       <c r="C797" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D797" t="n">
         <v>157</v>
@@ -13196,7 +13196,7 @@
         <v>4</v>
       </c>
       <c r="C798" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D798" t="n">
         <v>9</v>
@@ -13212,7 +13212,7 @@
         <v>4</v>
       </c>
       <c r="C799" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D799" t="n">
         <v>14</v>
@@ -13228,7 +13228,7 @@
         <v>4</v>
       </c>
       <c r="C800" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D800" t="n">
         <v>5</v>
@@ -13244,7 +13244,7 @@
         <v>5</v>
       </c>
       <c r="C801" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D801" t="n">
         <v>5</v>
@@ -13260,7 +13260,7 @@
         <v>5</v>
       </c>
       <c r="C802" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D802" t="n">
         <v>34</v>
@@ -13276,7 +13276,7 @@
         <v>5</v>
       </c>
       <c r="C803" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D803" t="n">
         <v>125</v>
@@ -13292,7 +13292,7 @@
         <v>5</v>
       </c>
       <c r="C804" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D804" t="n">
         <v>41</v>
@@ -13308,7 +13308,7 @@
         <v>5</v>
       </c>
       <c r="C805" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D805" t="n">
         <v>385</v>
@@ -13324,7 +13324,7 @@
         <v>5</v>
       </c>
       <c r="C806" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D806" t="n">
         <v>221</v>
@@ -13340,7 +13340,7 @@
         <v>5</v>
       </c>
       <c r="C807" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D807" t="n">
         <v>34</v>
@@ -13356,7 +13356,7 @@
         <v>6</v>
       </c>
       <c r="C808" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D808" t="n">
         <v>52</v>
@@ -13372,7 +13372,7 @@
         <v>6</v>
       </c>
       <c r="C809" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D809" t="n">
         <v>553</v>
@@ -13388,7 +13388,7 @@
         <v>6</v>
       </c>
       <c r="C810" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D810" t="n">
         <v>28</v>
@@ -13404,7 +13404,7 @@
         <v>6</v>
       </c>
       <c r="C811" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D811" t="n">
         <v>37</v>
@@ -13420,7 +13420,7 @@
         <v>6</v>
       </c>
       <c r="C812" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D812" t="n">
         <v>12</v>
@@ -13436,7 +13436,7 @@
         <v>7</v>
       </c>
       <c r="C813" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D813" t="n">
         <v>67</v>
@@ -13452,7 +13452,7 @@
         <v>7</v>
       </c>
       <c r="C814" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D814" t="n">
         <v>15</v>
@@ -13468,7 +13468,7 @@
         <v>7</v>
       </c>
       <c r="C815" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D815" t="n">
         <v>101</v>
@@ -13484,7 +13484,7 @@
         <v>7</v>
       </c>
       <c r="C816" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D816" t="n">
         <v>226</v>
@@ -13500,7 +13500,7 @@
         <v>7</v>
       </c>
       <c r="C817" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D817" t="n">
         <v>16</v>
@@ -13516,7 +13516,7 @@
         <v>8</v>
       </c>
       <c r="C818" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D818" t="n">
         <v>531</v>
@@ -13532,7 +13532,7 @@
         <v>8</v>
       </c>
       <c r="C819" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D819" t="n">
         <v>29</v>
@@ -13548,7 +13548,7 @@
         <v>8</v>
       </c>
       <c r="C820" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D820" t="n">
         <v>19</v>
@@ -13564,7 +13564,7 @@
         <v>8</v>
       </c>
       <c r="C821" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D821" t="n">
         <v>6</v>
